--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45461</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45824</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45680</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44902</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44610</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44896</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45908</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44498</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44699</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>45643</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44883</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45740</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45112</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>44699</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>45055</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45936</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45877</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>44487</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45790</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45755</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>45267</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>46084</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>45244</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45475</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45947</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>44896</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45726</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>45467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45204</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45740</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44610</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>46262</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45974</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>45973</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>46098</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>45908</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45530</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>45505</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45055</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>45505</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44497</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45671</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>45988</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45475</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45908</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>44505</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>45055</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>46154</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45974</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>45978</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45961</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45686</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>46073</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>45638</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45435</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>46217</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45467</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45961</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>44539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>45363</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45961</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44935</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>45608</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45931</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>45237</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45691</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>46171</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>45996</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>46198</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>45635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>44795</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45233</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>45961</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>46154</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45985</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45938</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45961</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44931</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>45971</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>45000</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45502</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>46086</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45604</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45471</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44904</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45615</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>44963</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>45055</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45961</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45309</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>45908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45853</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45985</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>46105</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45952</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>45961</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>45471</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45303</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>46001</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45233</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45011</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45848</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>46174</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45722</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45699</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45376</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45274</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45204</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>46269</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>44896</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>46055</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>46174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>46150</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45253</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45673</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45475</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45055</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45961</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45533</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44946</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>45973</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45974</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45877</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45303</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45939</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>46084</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>45924</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45740</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>46011</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>44931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45180</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>44887</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>45996</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45187</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>46189</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>46189</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>45611</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45611</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>46196</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>46199</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45898</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45666</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45194</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>46217</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45314</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45301</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>46199</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>46197</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>46238</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>46197</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>46066</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>44904</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>46086</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>46290</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45355</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>46035</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45834</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45590</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45135</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45274</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44812</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45635</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45455</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45552</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>44522</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45503</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45418</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>46259</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45321</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44848</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44851</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45777</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44845</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>44979</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45740</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45477</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>44943</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45201</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45937</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45937</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45471</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>46105</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>46105</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45958</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>46114</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45089</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45982</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45945</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45985</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>45555</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45140</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45992</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45238</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>46147</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45371</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>46147</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>46147</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45475</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45355</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>44467</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45121</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45688</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45722</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>46174</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45870</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45671</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44547</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>46205</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45376</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>46209</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44729</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45681</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45302</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45301</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46098</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45301</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45362</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44494</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>46196</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44904</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>44697</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>44904</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>44935</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45103</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45244</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45740</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45530</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45266</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>44699</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>45055</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>44981</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45435</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>45467</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45762</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>45722</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>45937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45937</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>46105</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>44467</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>44621</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>44480</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>44848</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>44848</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45468</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>46029</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>44848</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44944</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>46044</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>45917</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>45918</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45943</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44734</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>46105</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>46105</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>46105</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45266</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>45958</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45622</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45961</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45961</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45961</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45359</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>45089</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>45474</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45966</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44631</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>45980</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45982</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45677</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45782</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45918</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45831</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45931</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45936</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44830</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>45740</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44994</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>45754</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>45831</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45152</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45740</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>45754</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45336</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45121</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>45700</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>46175</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45688</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>46184</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45133</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45133</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>46184</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>44825</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45985</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -35283,7 +35283,7 @@
         <v>45148</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45700</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>45681</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45407</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>46266</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>46238</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44908</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>46240</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>46241</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>45740</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -36364,7 +36364,7 @@
         <v>45232</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>44979</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45604</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>44935</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>44931</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45625</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45740</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45253</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45338</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>44715</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44699</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>44596</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>45188</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45082</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45055</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>45384</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44981</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44469</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45055</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45531</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45385</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44494</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>45722</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45740</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>45740</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45789</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45809</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>45961</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>45961</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45961</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45965</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45966</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>46105</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46147</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>46177</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>46246</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44683</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>44820</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>44873</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>44650</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44512</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>44484</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>44582</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>44755</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44488</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44621</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>44546</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>44851</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>44673</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44785</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>44851</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>44504</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>44887</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44586</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>44861</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>44588</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>44564</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44511</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>44501</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>44825</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -42062,7 +42062,7 @@
         <v>44480</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>44565</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44848</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>44487</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>44812</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         <v>44545</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -42500,7 +42500,7 @@
         <v>44795</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>44796</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44565</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>44595</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>44756</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>44867</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -42938,7 +42938,7 @@
         <v>44825</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>44571</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44498</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
         <v>45194</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -43240,7 +43240,7 @@
         <v>45194</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -43318,7 +43318,7 @@
         <v>45327</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -43391,7 +43391,7 @@
         <v>45202</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45331</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45355</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>45187</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44930</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45379</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>44847</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>45036</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45379</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>45302</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45460</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45301</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45301</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>45117</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>45442</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>45454</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45086</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>45260</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>45240</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>44512</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>44861</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45256</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>44973</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>45258</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>46013</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>46013</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>46013</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>46013</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46013</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46020</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45512</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45512</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>44881</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45842</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45793</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>46029</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45483</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -46162,7 +46162,7 @@
         <v>44474</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>44946</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45530</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -46386,7 +46386,7 @@
         <v>45790</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>44466</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>46030</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>44937</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>46034</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>46034</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>46034</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>46034</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>45706</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45799</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>44564</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>44564</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>46037</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45635</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>44589</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45894</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45749</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -47637,7 +47637,7 @@
         <v>46044</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>45561</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>46044</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>46044</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>46042</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>46044</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>46044</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         <v>46044</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45393</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>46044</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>45460</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45535</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>45321</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -48591,7 +48591,7 @@
         <v>45701</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>44912</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -48742,7 +48742,7 @@
         <v>44912</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45625</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>44867</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>45538</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -49049,7 +49049,7 @@
         <v>46051</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>45272</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -49200,7 +49200,7 @@
         <v>46055</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>44964</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>44956</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45643</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>45287</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>46059</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>45511</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>44595</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>44672</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -49872,7 +49872,7 @@
         <v>45529</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45531</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45117</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>45358</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45379</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -50237,7 +50237,7 @@
         <v>45321</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>44973</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         <v>45604</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>45810</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>45807</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>44973</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>45589</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>45937</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>45211</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -50914,7 +50914,7 @@
         <v>45937</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45937</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -51070,7 +51070,7 @@
         <v>45937</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         <v>44904</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>44904</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>44904</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>45939</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45939</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -51523,7 +51523,7 @@
         <v>45533</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45576</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -51674,7 +51674,7 @@
         <v>44615</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45016</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45950</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>45950</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>45947</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -52039,7 +52039,7 @@
         <v>45566</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45950</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>45077</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45952</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -52331,7 +52331,7 @@
         <v>44994</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45953</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -52477,7 +52477,7 @@
         <v>45953</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45953</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -52623,7 +52623,7 @@
         <v>44970</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -52696,7 +52696,7 @@
         <v>45085</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -52774,7 +52774,7 @@
         <v>46113</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -52852,7 +52852,7 @@
         <v>46113</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -52925,7 +52925,7 @@
         <v>46113</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -52998,7 +52998,7 @@
         <v>45121</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -53071,7 +53071,7 @@
         <v>45671</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -53149,7 +53149,7 @@
         <v>45959</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -53227,7 +53227,7 @@
         <v>45460</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -53300,7 +53300,7 @@
         <v>44783</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -53373,7 +53373,7 @@
         <v>44956</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>45961</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45961</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>45961</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -53685,7 +53685,7 @@
         <v>44946</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>46126</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>44939</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -53904,7 +53904,7 @@
         <v>45265</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -53977,7 +53977,7 @@
         <v>45147</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -54050,7 +54050,7 @@
         <v>45971</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>45971</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>45968</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
         <v>45813</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>44487</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -54430,7 +54430,7 @@
         <v>44776</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -54503,7 +54503,7 @@
         <v>45245</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -54581,7 +54581,7 @@
         <v>45000</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>44720</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -54732,7 +54732,7 @@
         <v>46128</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45978</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -54883,7 +54883,7 @@
         <v>44964</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -54956,7 +54956,7 @@
         <v>46132</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>46132</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>44956</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45982</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>45985</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45642</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -55404,7 +55404,7 @@
         <v>45985</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45986</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -55555,7 +55555,7 @@
         <v>45754</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>45985</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         <v>45985</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>46029</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>44798</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -55925,7 +55925,7 @@
         <v>45986</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -56003,7 +56003,7 @@
         <v>45784</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>45985</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -56149,7 +56149,7 @@
         <v>45596</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -56222,7 +56222,7 @@
         <v>45988</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -56300,7 +56300,7 @@
         <v>45818</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -56373,7 +56373,7 @@
         <v>45988</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>45988</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>45842</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45204</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -56670,7 +56670,7 @@
         <v>45793</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -56743,7 +56743,7 @@
         <v>45931</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -56816,7 +56816,7 @@
         <v>45147</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45714</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -56967,7 +56967,7 @@
         <v>45622</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -57040,7 +57040,7 @@
         <v>45994</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45463</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -57191,7 +57191,7 @@
         <v>44748</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>44984</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -57342,7 +57342,7 @@
         <v>44984</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -57420,7 +57420,7 @@
         <v>45140</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45300</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>45939</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -57639,7 +57639,7 @@
         <v>45883</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -57712,7 +57712,7 @@
         <v>46001</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45945</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -57868,7 +57868,7 @@
         <v>46001</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>46001</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -58024,7 +58024,7 @@
         <v>45705</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45791</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>45035</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>46008</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -58321,7 +58321,7 @@
         <v>46008</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -58394,7 +58394,7 @@
         <v>46008</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>46008</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -58540,7 +58540,7 @@
         <v>44655</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -58613,7 +58613,7 @@
         <v>45804</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>46008</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>46008</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>44795</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -58905,7 +58905,7 @@
         <v>45819</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>45553</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>46008</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -59124,7 +59124,7 @@
         <v>46008</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45939</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45678</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45391</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45202</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -59494,7 +59494,7 @@
         <v>45483</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45817</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
         <v>44589</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -59713,7 +59713,7 @@
         <v>45553</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>45740</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -59864,7 +59864,7 @@
         <v>45240</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45201</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>45483</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -60083,7 +60083,7 @@
         <v>44851</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -60156,7 +60156,7 @@
         <v>45215</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -60229,7 +60229,7 @@
         <v>45747</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -60302,7 +60302,7 @@
         <v>44923</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -60375,7 +60375,7 @@
         <v>44923</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -60448,7 +60448,7 @@
         <v>45075</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -60521,7 +60521,7 @@
         <v>45825</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -60594,7 +60594,7 @@
         <v>46142</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -60672,7 +60672,7 @@
         <v>45723</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -60745,7 +60745,7 @@
         <v>44977</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -60818,7 +60818,7 @@
         <v>45068</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -60891,7 +60891,7 @@
         <v>45523</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>46099</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45076</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -61110,7 +61110,7 @@
         <v>45831</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>46141</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -61261,7 +61261,7 @@
         <v>45331</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -61339,7 +61339,7 @@
         <v>44848</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -61417,7 +61417,7 @@
         <v>45831</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -61490,7 +61490,7 @@
         <v>45754</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>44988</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -61641,7 +61641,7 @@
         <v>44971</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -61714,7 +61714,7 @@
         <v>45035</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -61787,7 +61787,7 @@
         <v>45076</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -61860,7 +61860,7 @@
         <v>46147</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>45371</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>45313</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -62084,7 +62084,7 @@
         <v>46147</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -62162,7 +62162,7 @@
         <v>44980</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>46147</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -62313,7 +62313,7 @@
         <v>46147</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -62391,7 +62391,7 @@
         <v>46147</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -62469,7 +62469,7 @@
         <v>45140</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -62542,7 +62542,7 @@
         <v>45831</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -62615,7 +62615,7 @@
         <v>44902</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -62688,7 +62688,7 @@
         <v>46120</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -62761,7 +62761,7 @@
         <v>45089</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -62834,7 +62834,7 @@
         <v>45793</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -62907,7 +62907,7 @@
         <v>45191</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -62985,7 +62985,7 @@
         <v>45391</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>45226</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -63141,7 +63141,7 @@
         <v>45740</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -63219,7 +63219,7 @@
         <v>45089</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -63292,7 +63292,7 @@
         <v>44651</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -63365,7 +63365,7 @@
         <v>46160</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -63443,7 +63443,7 @@
         <v>45740</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45740</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -63599,7 +63599,7 @@
         <v>46160</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         <v>46160</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -63755,7 +63755,7 @@
         <v>46160</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -63833,7 +63833,7 @@
         <v>46160</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -63911,7 +63911,7 @@
         <v>46160</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -63989,7 +63989,7 @@
         <v>45838</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>45104</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -64135,7 +64135,7 @@
         <v>45838</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -64208,7 +64208,7 @@
         <v>45049</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -64281,7 +64281,7 @@
         <v>45016</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -64354,7 +64354,7 @@
         <v>45196</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>45161</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -64505,7 +64505,7 @@
         <v>45159</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -64578,7 +64578,7 @@
         <v>44901</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -64651,7 +64651,7 @@
         <v>45330</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -64724,7 +64724,7 @@
         <v>45790</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -64797,7 +64797,7 @@
         <v>45390</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -64870,7 +64870,7 @@
         <v>45538</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -64943,7 +64943,7 @@
         <v>45848</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>44944</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -65089,7 +65089,7 @@
         <v>45873</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -65162,7 +65162,7 @@
         <v>44901</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -65235,7 +65235,7 @@
         <v>45847</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -65308,7 +65308,7 @@
         <v>45849</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -65381,7 +65381,7 @@
         <v>45719</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -65454,7 +65454,7 @@
         <v>45817</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -65527,7 +65527,7 @@
         <v>45853</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -65600,7 +65600,7 @@
         <v>44956</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -65673,7 +65673,7 @@
         <v>45201</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -65746,7 +65746,7 @@
         <v>45201</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -65819,7 +65819,7 @@
         <v>45198</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -65892,7 +65892,7 @@
         <v>44910</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -65970,7 +65970,7 @@
         <v>45093</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -66043,7 +66043,7 @@
         <v>45783</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -66116,7 +66116,7 @@
         <v>46175</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -66189,7 +66189,7 @@
         <v>44977</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -66262,7 +66262,7 @@
         <v>44552</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -66335,7 +66335,7 @@
         <v>45722</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -66408,7 +66408,7 @@
         <v>44820</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -66481,7 +66481,7 @@
         <v>45306</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -66554,7 +66554,7 @@
         <v>45306</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -66627,7 +66627,7 @@
         <v>44973</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45035</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -66773,7 +66773,7 @@
         <v>44977</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -66846,7 +66846,7 @@
         <v>45566</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>44910</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -66992,7 +66992,7 @@
         <v>44468</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -67065,7 +67065,7 @@
         <v>44621</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -67138,7 +67138,7 @@
         <v>46183</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -67211,7 +67211,7 @@
         <v>45484</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -67284,7 +67284,7 @@
         <v>45775</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -67357,7 +67357,7 @@
         <v>44977</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -67430,7 +67430,7 @@
         <v>45148</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45644</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -67586,7 +67586,7 @@
         <v>46184</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -67664,7 +67664,7 @@
         <v>46184</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -67742,7 +67742,7 @@
         <v>46188</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -67815,7 +67815,7 @@
         <v>45133</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -67888,7 +67888,7 @@
         <v>45671</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -67966,7 +67966,7 @@
         <v>45170</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -68039,7 +68039,7 @@
         <v>45170</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -68112,7 +68112,7 @@
         <v>45630</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -68185,7 +68185,7 @@
         <v>46184</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -68263,7 +68263,7 @@
         <v>46184</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -68341,7 +68341,7 @@
         <v>46184</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -68419,7 +68419,7 @@
         <v>46189</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -68492,7 +68492,7 @@
         <v>46189</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -68565,7 +68565,7 @@
         <v>46189</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -68638,7 +68638,7 @@
         <v>45160</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -68716,7 +68716,7 @@
         <v>45537</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -68794,7 +68794,7 @@
         <v>46190</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -68867,7 +68867,7 @@
         <v>46195</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -68940,7 +68940,7 @@
         <v>46195</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -69013,7 +69013,7 @@
         <v>45916</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -69086,7 +69086,7 @@
         <v>46195</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -69179,7 +69179,7 @@
         <v>45678</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -69272,7 +69272,7 @@
         <v>46197</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -69345,7 +69345,7 @@
         <v>45673</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -69418,7 +69418,7 @@
         <v>46197</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -69491,7 +69491,7 @@
         <v>45877</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -69564,7 +69564,7 @@
         <v>45068</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -69637,7 +69637,7 @@
         <v>45671</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -69715,7 +69715,7 @@
         <v>46199</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -69793,7 +69793,7 @@
         <v>45478</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -69866,7 +69866,7 @@
         <v>45468</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -69939,7 +69939,7 @@
         <v>45468</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -70012,7 +70012,7 @@
         <v>45635</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -70085,7 +70085,7 @@
         <v>44646</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -70158,7 +70158,7 @@
         <v>46199</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -70236,7 +70236,7 @@
         <v>45706</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -70309,7 +70309,7 @@
         <v>46202</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -70382,7 +70382,7 @@
         <v>46205</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -70455,7 +70455,7 @@
         <v>46205</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -70528,7 +70528,7 @@
         <v>46205</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -70606,7 +70606,7 @@
         <v>45477</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -70684,7 +70684,7 @@
         <v>46249</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -70762,7 +70762,7 @@
         <v>45621</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -70840,7 +70840,7 @@
         <v>46252</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -70913,7 +70913,7 @@
         <v>45049</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -70986,7 +70986,7 @@
         <v>46029</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -71059,7 +71059,7 @@
         <v>45945</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -71132,7 +71132,7 @@
         <v>45755</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -71205,7 +71205,7 @@
         <v>45093</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -71278,7 +71278,7 @@
         <v>45093</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -71351,7 +71351,7 @@
         <v>45093</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -71424,7 +71424,7 @@
         <v>46251</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -71497,7 +71497,7 @@
         <v>45196</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>44669</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>46253</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -71721,7 +71721,7 @@
         <v>45240</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -71794,7 +71794,7 @@
         <v>46209</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -71867,7 +71867,7 @@
         <v>45147</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -71940,7 +71940,7 @@
         <v>44573</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -72018,7 +72018,7 @@
         <v>45245</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -72096,7 +72096,7 @@
         <v>45148</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -72174,7 +72174,7 @@
         <v>44623</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -72252,7 +72252,7 @@
         <v>44635</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -72325,7 +72325,7 @@
         <v>46217</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -72398,7 +72398,7 @@
         <v>46217</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -72471,7 +72471,7 @@
         <v>45239</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -72544,7 +72544,7 @@
         <v>46259</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -72622,7 +72622,7 @@
         <v>45147</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -72700,7 +72700,7 @@
         <v>46217</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -72773,7 +72773,7 @@
         <v>46217</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -72846,7 +72846,7 @@
         <v>46217</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -72919,7 +72919,7 @@
         <v>46217</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -72992,7 +72992,7 @@
         <v>45153</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -73065,7 +73065,7 @@
         <v>45236</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -73138,7 +73138,7 @@
         <v>46262</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -73216,7 +73216,7 @@
         <v>46217</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -73289,7 +73289,7 @@
         <v>46262</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -73367,7 +73367,7 @@
         <v>45211</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -73445,7 +73445,7 @@
         <v>46261</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -73523,7 +73523,7 @@
         <v>46261</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -73601,7 +73601,7 @@
         <v>46261</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -73679,7 +73679,7 @@
         <v>46261</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -73757,7 +73757,7 @@
         <v>46262</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -73835,7 +73835,7 @@
         <v>46262</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -73913,7 +73913,7 @@
         <v>45251</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -73991,7 +73991,7 @@
         <v>46262</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -74069,7 +74069,7 @@
         <v>46261</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -74147,7 +74147,7 @@
         <v>46261</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -74225,7 +74225,7 @@
         <v>46261</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -74303,7 +74303,7 @@
         <v>46262</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -74381,7 +74381,7 @@
         <v>46262</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -74459,7 +74459,7 @@
         <v>46262</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -74537,7 +74537,7 @@
         <v>46262</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -74615,7 +74615,7 @@
         <v>45722</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -74688,7 +74688,7 @@
         <v>44722</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -74761,7 +74761,7 @@
         <v>45159</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -74834,7 +74834,7 @@
         <v>45236</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -74912,7 +74912,7 @@
         <v>45216</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -74985,7 +74985,7 @@
         <v>45110</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -75063,7 +75063,7 @@
         <v>45261</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -75141,7 +75141,7 @@
         <v>46221</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -75214,7 +75214,7 @@
         <v>45525</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -75292,7 +75292,7 @@
         <v>45272</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -75365,7 +75365,7 @@
         <v>45680</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -75438,7 +75438,7 @@
         <v>45336</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -75511,7 +75511,7 @@
         <v>45237</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -75584,7 +75584,7 @@
         <v>45309</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -75657,7 +75657,7 @@
         <v>45369</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -75730,7 +75730,7 @@
         <v>44811</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -75803,7 +75803,7 @@
         <v>45237</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -75876,7 +75876,7 @@
         <v>44785</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -75949,7 +75949,7 @@
         <v>44785</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -76022,7 +76022,7 @@
         <v>46272</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -76095,7 +76095,7 @@
         <v>45366</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -76173,7 +76173,7 @@
         <v>46269</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -76246,7 +76246,7 @@
         <v>45196</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -76324,7 +76324,7 @@
         <v>45196</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -76402,7 +76402,7 @@
         <v>45240</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -76475,7 +76475,7 @@
         <v>45477</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -76553,7 +76553,7 @@
         <v>45477</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -76631,7 +76631,7 @@
         <v>45301</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -76704,7 +76704,7 @@
         <v>45301</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -76777,7 +76777,7 @@
         <v>46272</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -76850,7 +76850,7 @@
         <v>46272</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -76923,7 +76923,7 @@
         <v>45089</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -76996,7 +76996,7 @@
         <v>45040</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -77069,7 +77069,7 @@
         <v>45301</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -77142,7 +77142,7 @@
         <v>45114</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -77215,7 +77215,7 @@
         <v>45278</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -77288,7 +77288,7 @@
         <v>45362</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -77361,7 +77361,7 @@
         <v>46279</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -77434,7 +77434,7 @@
         <v>46234</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -77512,7 +77512,7 @@
         <v>45301</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -77585,7 +77585,7 @@
         <v>44509</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -77658,7 +77658,7 @@
         <v>45637</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -77731,7 +77731,7 @@
         <v>46238</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -77804,7 +77804,7 @@
         <v>45631</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -77877,7 +77877,7 @@
         <v>46239</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -77950,7 +77950,7 @@
         <v>46238</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -78023,7 +78023,7 @@
         <v>46238</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -78096,7 +78096,7 @@
         <v>46238</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -78169,7 +78169,7 @@
         <v>46238</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -78242,7 +78242,7 @@
         <v>46238</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -78315,7 +78315,7 @@
         <v>44935</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -78388,7 +78388,7 @@
         <v>46238</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -78461,7 +78461,7 @@
         <v>44901</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -78534,7 +78534,7 @@
         <v>45671</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -78607,7 +78607,7 @@
         <v>45033</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -78680,7 +78680,7 @@
         <v>46286</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -78753,7 +78753,7 @@
         <v>46183</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -78826,7 +78826,7 @@
         <v>44916</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -78899,7 +78899,7 @@
         <v>44893</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -78972,7 +78972,7 @@
         <v>46282</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -79045,7 +79045,7 @@
         <v>45951</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -79118,7 +79118,7 @@
         <v>44848</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -79191,7 +79191,7 @@
         <v>44867</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -79269,7 +79269,7 @@
         <v>45489</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -79342,7 +79342,7 @@
         <v>44904</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -79415,7 +79415,7 @@
         <v>44904</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -79488,7 +79488,7 @@
         <v>45174</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -79561,7 +79561,7 @@
         <v>44646</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -79634,7 +79634,7 @@
         <v>44960</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -79707,7 +79707,7 @@
         <v>44480</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -79780,7 +79780,7 @@
         <v>46246</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -79853,7 +79853,7 @@
         <v>46150</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -79926,7 +79926,7 @@
         <v>45301</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -79999,7 +79999,7 @@
         <v>45140</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -80072,7 +80072,7 @@
         <v>44987</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -80145,7 +80145,7 @@
         <v>44623</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -80223,7 +80223,7 @@
         <v>44916</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -80301,7 +80301,7 @@
         <v>46035</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -80374,7 +80374,7 @@
         <v>46290</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -80452,7 +80452,7 @@
         <v>46175</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -80525,7 +80525,7 @@
         <v>44963</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -80603,7 +80603,7 @@
         <v>46105</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -80681,7 +80681,7 @@
         <v>45256</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -80759,7 +80759,7 @@
         <v>45343</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -80832,7 +80832,7 @@
         <v>45204</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -80905,7 +80905,7 @@
         <v>46048</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -80978,7 +80978,7 @@
         <v>46290</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -81056,7 +81056,7 @@
         <v>46290</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -81134,7 +81134,7 @@
         <v>44848</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -81212,7 +81212,7 @@
         <v>45764</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -81285,7 +81285,7 @@
         <v>45673</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -81358,7 +81358,7 @@
         <v>45040</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -81436,7 +81436,7 @@
         <v>45104</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -81509,7 +81509,7 @@
         <v>44468</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -81582,7 +81582,7 @@
         <v>45021</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -81655,7 +81655,7 @@
         <v>45740</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -81733,7 +81733,7 @@
         <v>45222</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -81806,7 +81806,7 @@
         <v>44532</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -81879,7 +81879,7 @@
         <v>44964</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -81957,7 +81957,7 @@
         <v>45016</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -82030,7 +82030,7 @@
         <v>44539</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -82103,7 +82103,7 @@
         <v>44924</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -82176,7 +82176,7 @@
         <v>45282</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -82254,7 +82254,7 @@
         <v>45282</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -82332,7 +82332,7 @@
         <v>45540</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -82410,7 +82410,7 @@
         <v>44977</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -82483,7 +82483,7 @@
         <v>44977</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -82556,7 +82556,7 @@
         <v>45374</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -82629,7 +82629,7 @@
         <v>45681</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -82702,7 +82702,7 @@
         <v>45160</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -82780,7 +82780,7 @@
         <v>45036</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -82853,7 +82853,7 @@
         <v>45104</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -82931,7 +82931,7 @@
         <v>45160</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -83009,7 +83009,7 @@
         <v>45610</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -83087,7 +83087,7 @@
         <v>44929</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -83160,7 +83160,7 @@
         <v>44484</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -83233,7 +83233,7 @@
         <v>44908</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -83306,7 +83306,7 @@
         <v>45068</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -83379,7 +83379,7 @@
         <v>44942</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -83452,7 +83452,7 @@
         <v>45160</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -83530,7 +83530,7 @@
         <v>45622</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -83603,7 +83603,7 @@
         <v>44785</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -83676,7 +83676,7 @@
         <v>44641</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -83754,7 +83754,7 @@
         <v>45035</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -83827,7 +83827,7 @@
         <v>45253</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -83900,7 +83900,7 @@
         <v>45147</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -83973,7 +83973,7 @@
         <v>45022</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -84051,7 +84051,7 @@
         <v>45643</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -84124,7 +84124,7 @@
         <v>45012</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -84197,7 +84197,7 @@
         <v>45590</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -84270,7 +84270,7 @@
         <v>45455</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -84348,7 +84348,7 @@
         <v>45460</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -84421,7 +84421,7 @@
         <v>44989</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -84494,7 +84494,7 @@
         <v>44979</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -84567,7 +84567,7 @@
         <v>45448</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -84645,7 +84645,7 @@
         <v>44783</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -84718,7 +84718,7 @@
         <v>44728</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -84791,7 +84791,7 @@
         <v>45631</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -84864,7 +84864,7 @@
         <v>45414</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -84937,7 +84937,7 @@
         <v>45743</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -85010,7 +85010,7 @@
         <v>45148</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -85088,7 +85088,7 @@
         <v>45567</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -85161,7 +85161,7 @@
         <v>44960</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -85234,7 +85234,7 @@
         <v>44979</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -85307,7 +85307,7 @@
         <v>45215</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -85380,7 +85380,7 @@
         <v>45003</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -85473,7 +85473,7 @@
         <v>44979</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -85546,7 +85546,7 @@
         <v>44532</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -85619,7 +85619,7 @@
         <v>44785</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -85692,7 +85692,7 @@
         <v>45371</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -85765,7 +85765,7 @@
         <v>44888</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -85838,7 +85838,7 @@
         <v>45611</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -85916,7 +85916,7 @@
         <v>45477</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -85989,7 +85989,7 @@
         <v>44756</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -86062,7 +86062,7 @@
         <v>45694</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -86135,7 +86135,7 @@
         <v>45036</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -86208,7 +86208,7 @@
         <v>45596</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -86281,7 +86281,7 @@
         <v>45160</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -86354,7 +86354,7 @@
         <v>45740</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -86432,7 +86432,7 @@
         <v>45551</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -86505,7 +86505,7 @@
         <v>45777</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -86578,7 +86578,7 @@
         <v>45476</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -86651,7 +86651,7 @@
         <v>45625</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -86729,7 +86729,7 @@
         <v>45604</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -86807,7 +86807,7 @@
         <v>44698</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -86880,7 +86880,7 @@
         <v>44711</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -86953,7 +86953,7 @@
         <v>44671</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -87026,7 +87026,7 @@
         <v>45631</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -87099,7 +87099,7 @@
         <v>45525</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -87172,7 +87172,7 @@
         <v>45055</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -87250,7 +87250,7 @@
         <v>45061</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -87323,7 +87323,7 @@
         <v>45531</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -87401,7 +87401,7 @@
         <v>44783</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -87479,7 +87479,7 @@
         <v>44468</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -87552,7 +87552,7 @@
         <v>45545</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -87630,7 +87630,7 @@
         <v>44469</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -87703,7 +87703,7 @@
         <v>45467</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -87781,7 +87781,7 @@
         <v>44487</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -87859,7 +87859,7 @@
         <v>45670</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -87932,7 +87932,7 @@
         <v>45351</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -88010,7 +88010,7 @@
         <v>45371</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -88088,7 +88088,7 @@
         <v>45371</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -88166,7 +88166,7 @@
         <v>45637</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -88239,7 +88239,7 @@
         <v>45525</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -88317,7 +88317,7 @@
         <v>45604</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -88390,7 +88390,7 @@
         <v>45341</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -88463,7 +88463,7 @@
         <v>45422</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -88541,7 +88541,7 @@
         <v>45587</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -88614,7 +88614,7 @@
         <v>45332</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -88687,7 +88687,7 @@
         <v>45222</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -88760,7 +88760,7 @@
         <v>44494</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -88833,7 +88833,7 @@
         <v>45785</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -88906,7 +88906,7 @@
         <v>45797</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -88979,7 +88979,7 @@
         <v>45821</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -89052,7 +89052,7 @@
         <v>45834</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -89130,7 +89130,7 @@
         <v>45848</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -89203,7 +89203,7 @@
         <v>45937</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -89281,7 +89281,7 @@
         <v>45937</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -89359,7 +89359,7 @@
         <v>45961</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -89437,7 +89437,7 @@
         <v>45961</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -89515,7 +89515,7 @@
         <v>45961</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -89593,7 +89593,7 @@
         <v>44706</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -89666,7 +89666,7 @@
         <v>46057</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -89744,7 +89744,7 @@
         <v>46085</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -89822,7 +89822,7 @@
         <v>46094</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -89900,7 +89900,7 @@
         <v>46191</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -89978,7 +89978,7 @@
         <v>46262</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -90056,7 +90056,7 @@
         <v>46262</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -90134,7 +90134,7 @@
         <v>46270</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -90207,7 +90207,7 @@
         <v>46246</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45461</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45824</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>45680</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>44902</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44610</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>44896</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45908</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44498</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44699</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>45643</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>44883</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45112</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>44699</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>45055</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45936</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45877</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>44487</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45790</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45755</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>45475</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45726</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>45244</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>46084</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>44896</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>45947</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>45531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45204</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45740</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>44610</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>46262</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>45671</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>45530</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>46098</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>45908</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45973</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>45974</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>45505</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>45055</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>45505</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>46259</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44497</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>44505</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45671</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>45988</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45475</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>45908</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45055</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>46154</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45961</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>45686</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>46073</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45638</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44868</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45435</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>46293</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45974</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45978</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>45467</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>45961</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>44539</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44795</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45677</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45363</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45961</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>44935</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>45931</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45608</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>46171</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>45691</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45635</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45237</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45996</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45233</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>45961</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>46154</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45000</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45985</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45938</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>45961</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45971</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45604</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45502</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>46086</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44904</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45471</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>46279</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44931</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>45615</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44963</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45055</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45961</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>46001</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45309</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45673</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45853</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>45908</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45985</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45274</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>45475</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45376</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45952</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45961</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>45471</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>46105</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>45471</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>45303</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45848</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45011</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>46174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45699</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45722</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>46269</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44896</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45204</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>46199</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>46174</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45233</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45253</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45055</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45961</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45635</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>44931</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>46011</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>44887</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45355</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45877</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45303</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>45939</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45666</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>46084</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45590</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45135</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>44946</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45924</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45740</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45314</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45611</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45611</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>46189</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>46196</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>46199</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>45898</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>46217</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45266</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>46197</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45194</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>46066</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46086</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>45834</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>45274</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>46238</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>46035</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45996</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>46290</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>45533</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45973</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>45301</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>45974</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45187</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45180</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>44812</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>44904</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45455</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45552</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>44522</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45503</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45418</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45103</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44904</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45777</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45937</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45937</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45671</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45477</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>45681</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45958</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44848</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>46105</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>46105</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45982</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45985</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>45302</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>46114</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44935</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45992</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>44547</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>44943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45121</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44851</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45945</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45555</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45321</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45870</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>46147</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>46147</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45371</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45475</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45301</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>46174</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45688</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45740</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45740</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45722</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>44697</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44979</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45376</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>46209</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>44845</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45355</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>46098</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45301</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44729</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45244</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>45201</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>46205</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45362</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>46296</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45140</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>45238</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45089</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27234,7 +27234,7 @@
         <v>44494</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>44904</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>45530</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45266</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45055</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>44981</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45435</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>44699</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>45467</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45762</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45722</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>45937</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45937</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>46105</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>44621</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44480</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>44825</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45740</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>44734</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44830</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>45936</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45336</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>44931</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45917</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>45918</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45958</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45961</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45468</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45961</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45961</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>45966</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>45359</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>46105</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>46105</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>46105</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>44944</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45980</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>45982</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>45474</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>44908</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45831</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>45622</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45677</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45918</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45407</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45782</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>45253</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45931</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45831</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>44935</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45232</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>44994</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45754</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>45754</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44848</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>45121</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45700</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>46175</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45688</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45700</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>46184</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>46184</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45266</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45148</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>45740</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45985</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45152</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45133</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>45133</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>46266</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>45068</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>46238</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>46240</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45604</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45740</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>46241</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>46029</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>46044</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45740</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45681</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>45625</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>44631</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44848</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44848</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>44979</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45089</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45338</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45188</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45082</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45055</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45384</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>44981</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>44715</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45055</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>45531</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>45385</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44699</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>44494</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>44596</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45722</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45740</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>45740</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>45789</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45809</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45961</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45961</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45961</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>45965</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45966</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -39093,7 +39093,7 @@
         <v>46105</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46147</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>46177</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>46246</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>44683</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>44820</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>44873</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44512</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44650</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>44484</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>44582</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>44755</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>44488</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>44621</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44546</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>44851</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44673</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>44851</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>44785</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -40632,7 +40632,7 @@
         <v>44504</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>44887</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>44586</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>44861</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>44588</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>44564</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44511</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>44501</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>44825</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>44480</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>44565</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>44848</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>44487</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44812</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>44545</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>44795</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>44796</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>44595</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>44565</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44756</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>44867</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>44825</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>44571</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44498</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>45460</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45147</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45531</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45251</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>44595</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45174</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45643</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45196</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>45525</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45012</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -43149,7 +43149,7 @@
         <v>45033</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>45021</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>45278</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45722</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45642</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45260</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44937</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45379</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45211</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>45211</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>44532</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>45191</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>44946</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>45764</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>46001</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>45093</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45093</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45093</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45625</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>45114</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>44623</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>44973</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45282</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -44868,7 +44868,7 @@
         <v>45282</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>46001</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>46001</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44783</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45237</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45533</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>46008</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>46008</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -45472,7 +45472,7 @@
         <v>45240</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>44901</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>46008</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -45691,7 +45691,7 @@
         <v>46008</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>44960</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>46008</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -45910,7 +45910,7 @@
         <v>46008</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45358</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>46008</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>46008</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>45596</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45309</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>45016</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45140</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>46013</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>46013</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>46013</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>46013</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>46013</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>46020</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45842</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45894</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>45631</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>46030</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45511</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>46034</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>46034</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44910</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>46034</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>46034</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45701</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45567</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45793</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>44904</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -47994,7 +47994,7 @@
         <v>46042</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45790</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -48140,7 +48140,7 @@
         <v>46044</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>46044</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>46044</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -48359,7 +48359,7 @@
         <v>46044</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>46044</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>46044</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -48578,7 +48578,7 @@
         <v>46044</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -48651,7 +48651,7 @@
         <v>45256</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>45749</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>45561</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -48880,7 +48880,7 @@
         <v>45799</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -48953,7 +48953,7 @@
         <v>45706</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -49026,7 +49026,7 @@
         <v>46051</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -49104,7 +49104,7 @@
         <v>45393</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>45287</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>44956</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -49328,7 +49328,7 @@
         <v>45245</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45222</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>46055</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -49552,7 +49552,7 @@
         <v>45807</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45147</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>44977</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -49771,7 +49771,7 @@
         <v>44988</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45576</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>46059</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45460</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -50063,7 +50063,7 @@
         <v>45460</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>44901</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -50209,7 +50209,7 @@
         <v>45937</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>45937</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -50365,7 +50365,7 @@
         <v>45939</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>45937</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>45939</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45671</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>45236</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45239</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>44902</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45160</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45147</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>45678</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45947</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45226</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>45950</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>45810</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>45950</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45950</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -51578,7 +51578,7 @@
         <v>45673</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>45196</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -51729,7 +51729,7 @@
         <v>45953</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -51802,7 +51802,7 @@
         <v>45953</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45952</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45953</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -52021,7 +52021,7 @@
         <v>45813</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45959</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -52172,7 +52172,7 @@
         <v>45075</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45003</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -52338,7 +52338,7 @@
         <v>45036</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45000</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>45961</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45961</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>45961</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -52723,7 +52723,7 @@
         <v>44811</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -52796,7 +52796,7 @@
         <v>44484</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>45671</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>44960</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -53020,7 +53020,7 @@
         <v>45971</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>44785</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>45968</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45971</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -53327,7 +53327,7 @@
         <v>44573</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45635</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>44970</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -53551,7 +53551,7 @@
         <v>44776</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         <v>45016</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45201</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45201</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45631</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>45483</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -53989,7 +53989,7 @@
         <v>45978</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45566</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>44615</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45336</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         <v>44785</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>45240</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -54432,7 +54432,7 @@
         <v>45982</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45985</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>45819</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45529</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>45985</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>45035</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -54870,7 +54870,7 @@
         <v>45985</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45985</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>45985</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>46113</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>46113</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>45986</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>45986</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45825</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>46113</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -55542,7 +55542,7 @@
         <v>44532</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -55615,7 +55615,7 @@
         <v>45202</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -55688,7 +55688,7 @@
         <v>45159</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45694</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45988</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -55907,7 +55907,7 @@
         <v>45331</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>44881</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -56058,7 +56058,7 @@
         <v>45147</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>46126</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -56209,7 +56209,7 @@
         <v>45160</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>45994</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -56360,7 +56360,7 @@
         <v>44944</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45117</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45369</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>46128</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -56652,7 +56652,7 @@
         <v>45831</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45831</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45159</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>44552</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>46132</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -57022,7 +57022,7 @@
         <v>46132</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45477</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -57178,7 +57178,7 @@
         <v>45477</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -57256,7 +57256,7 @@
         <v>45201</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -57329,7 +57329,7 @@
         <v>45530</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>44635</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -57480,7 +57480,7 @@
         <v>45793</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>45671</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -57631,7 +57631,7 @@
         <v>44798</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>44669</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -57777,7 +57777,7 @@
         <v>45454</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -57850,7 +57850,7 @@
         <v>44847</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -57923,7 +57923,7 @@
         <v>45622</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -57996,7 +57996,7 @@
         <v>45945</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>45160</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -58152,7 +58152,7 @@
         <v>45838</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -58225,7 +58225,7 @@
         <v>44994</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         <v>45754</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>45818</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -58449,7 +58449,7 @@
         <v>45838</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -58522,7 +58522,7 @@
         <v>45931</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>44748</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>45040</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45093</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -58824,7 +58824,7 @@
         <v>44923</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -58897,7 +58897,7 @@
         <v>44923</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45035</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -59043,7 +59043,7 @@
         <v>45300</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>44646</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -59189,7 +59189,7 @@
         <v>45790</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -59262,7 +59262,7 @@
         <v>46029</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>44912</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>45483</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>45793</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>45621</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -59637,7 +59637,7 @@
         <v>45847</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -59710,7 +59710,7 @@
         <v>45301</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -59783,7 +59783,7 @@
         <v>45848</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -59856,7 +59856,7 @@
         <v>45272</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -59929,7 +59929,7 @@
         <v>45849</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -60002,7 +60002,7 @@
         <v>45817</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>44964</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>45719</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -60226,7 +60226,7 @@
         <v>45939</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -60299,7 +60299,7 @@
         <v>45104</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>45553</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>45853</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -60518,7 +60518,7 @@
         <v>45076</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>45681</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>45611</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -60742,7 +60742,7 @@
         <v>45089</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>45791</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45883</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45804</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>45489</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>45714</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>45463</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>45939</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>45553</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -61409,7 +61409,7 @@
         <v>45391</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>45740</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>45817</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -61638,7 +61638,7 @@
         <v>45784</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>45622</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>45035</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>45842</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>44916</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>44971</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>46099</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>45253</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -62227,7 +62227,7 @@
         <v>45523</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -62300,7 +62300,7 @@
         <v>44646</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>45643</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -62446,7 +62446,7 @@
         <v>45783</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>44848</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>44848</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -62670,7 +62670,7 @@
         <v>45240</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -62743,7 +62743,7 @@
         <v>45302</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -62816,7 +62816,7 @@
         <v>45538</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -62889,7 +62889,7 @@
         <v>44977</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -62962,7 +62962,7 @@
         <v>44977</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -63035,7 +63035,7 @@
         <v>46141</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -63113,7 +63113,7 @@
         <v>45049</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -63186,7 +63186,7 @@
         <v>44979</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -63259,7 +63259,7 @@
         <v>44904</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -63332,7 +63332,7 @@
         <v>45740</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -63410,7 +63410,7 @@
         <v>45740</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>45535</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>45330</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -63634,7 +63634,7 @@
         <v>46142</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>45590</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -63785,7 +63785,7 @@
         <v>45161</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -63858,7 +63858,7 @@
         <v>45414</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>45313</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -64004,7 +64004,7 @@
         <v>46147</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>46147</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -64160,7 +64160,7 @@
         <v>46147</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -64238,7 +64238,7 @@
         <v>46147</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -64316,7 +64316,7 @@
         <v>45644</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -64394,7 +64394,7 @@
         <v>44980</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -64467,7 +64467,7 @@
         <v>46147</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -64545,7 +64545,7 @@
         <v>45371</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -64618,7 +64618,7 @@
         <v>45215</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -64691,7 +64691,7 @@
         <v>45775</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -64764,7 +64764,7 @@
         <v>45673</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         <v>44956</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -64910,7 +64910,7 @@
         <v>45754</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         <v>45630</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>45604</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -65139,7 +65139,7 @@
         <v>44977</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -65212,7 +65212,7 @@
         <v>46120</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -65285,7 +65285,7 @@
         <v>45215</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         <v>45391</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>44641</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -65514,7 +65514,7 @@
         <v>45237</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -65587,7 +65587,7 @@
         <v>44820</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -65660,7 +65660,7 @@
         <v>44795</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -65733,7 +65733,7 @@
         <v>44848</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -65811,7 +65811,7 @@
         <v>45327</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -65884,7 +65884,7 @@
         <v>45148</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -65962,7 +65962,7 @@
         <v>45343</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -66035,7 +66035,7 @@
         <v>46160</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>46160</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -66191,7 +66191,7 @@
         <v>46160</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -66269,7 +66269,7 @@
         <v>46160</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -66347,7 +66347,7 @@
         <v>46160</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -66425,7 +66425,7 @@
         <v>46160</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -66503,7 +66503,7 @@
         <v>45877</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -66576,7 +66576,7 @@
         <v>45371</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -66649,7 +66649,7 @@
         <v>44935</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -66722,7 +66722,7 @@
         <v>45706</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -66795,7 +66795,7 @@
         <v>45301</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -66868,7 +66868,7 @@
         <v>45301</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -66941,7 +66941,7 @@
         <v>45355</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -67014,7 +67014,7 @@
         <v>45873</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -67087,7 +67087,7 @@
         <v>44956</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -67165,7 +67165,7 @@
         <v>45068</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -67238,7 +67238,7 @@
         <v>45160</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -67316,7 +67316,7 @@
         <v>45478</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45140</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -67462,7 +67462,7 @@
         <v>45538</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -67535,7 +67535,7 @@
         <v>45455</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -67613,7 +67613,7 @@
         <v>45265</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -67686,7 +67686,7 @@
         <v>45722</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -67759,7 +67759,7 @@
         <v>46175</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -67832,7 +67832,7 @@
         <v>44474</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -67905,7 +67905,7 @@
         <v>44480</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -67978,7 +67978,7 @@
         <v>45566</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -68051,7 +68051,7 @@
         <v>44728</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -68124,7 +68124,7 @@
         <v>44939</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -68197,7 +68197,7 @@
         <v>46184</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -68275,7 +68275,7 @@
         <v>46184</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -68353,7 +68353,7 @@
         <v>46184</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -68431,7 +68431,7 @@
         <v>46184</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -68509,7 +68509,7 @@
         <v>46184</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -68587,7 +68587,7 @@
         <v>44930</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -68660,7 +68660,7 @@
         <v>45589</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -68733,7 +68733,7 @@
         <v>46188</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -68806,7 +68806,7 @@
         <v>46190</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -68879,7 +68879,7 @@
         <v>44621</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -68952,7 +68952,7 @@
         <v>46189</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -69025,7 +69025,7 @@
         <v>46189</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -69098,7 +69098,7 @@
         <v>45036</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -69171,7 +69171,7 @@
         <v>45272</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -69244,7 +69244,7 @@
         <v>45916</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -69317,7 +69317,7 @@
         <v>45678</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -69390,7 +69390,7 @@
         <v>46197</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -69463,7 +69463,7 @@
         <v>46195</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -69536,7 +69536,7 @@
         <v>46195</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -69609,7 +69609,7 @@
         <v>45204</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -69682,7 +69682,7 @@
         <v>45740</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -69760,7 +69760,7 @@
         <v>45198</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -69833,7 +69833,7 @@
         <v>45390</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -69906,7 +69906,7 @@
         <v>46197</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -69979,7 +69979,7 @@
         <v>45484</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -70052,7 +70052,7 @@
         <v>44956</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -70125,7 +70125,7 @@
         <v>46199</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -70203,7 +70203,7 @@
         <v>46199</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -70281,7 +70281,7 @@
         <v>46202</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -70354,7 +70354,7 @@
         <v>45086</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -70427,7 +70427,7 @@
         <v>45261</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -70505,7 +70505,7 @@
         <v>45483</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -70578,7 +70578,7 @@
         <v>45170</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -70651,7 +70651,7 @@
         <v>45170</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -70724,7 +70724,7 @@
         <v>45121</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -70797,7 +70797,7 @@
         <v>46205</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -70870,7 +70870,7 @@
         <v>46205</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -70948,7 +70948,7 @@
         <v>45945</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -71021,7 +71021,7 @@
         <v>46205</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -71094,7 +71094,7 @@
         <v>44893</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -71167,7 +71167,7 @@
         <v>46029</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -71240,7 +71240,7 @@
         <v>45477</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -71318,7 +71318,7 @@
         <v>44942</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -71391,7 +71391,7 @@
         <v>45148</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -71469,7 +71469,7 @@
         <v>44973</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -71542,7 +71542,7 @@
         <v>44861</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -71615,7 +71615,7 @@
         <v>45245</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -71693,7 +71693,7 @@
         <v>46259</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -71771,7 +71771,7 @@
         <v>44973</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -71844,7 +71844,7 @@
         <v>45202</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -71917,7 +71917,7 @@
         <v>45133</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -71990,7 +71990,7 @@
         <v>46261</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -72068,7 +72068,7 @@
         <v>44977</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -72141,7 +72141,7 @@
         <v>46217</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -72214,7 +72214,7 @@
         <v>46261</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -72292,7 +72292,7 @@
         <v>45366</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -72370,7 +72370,7 @@
         <v>46261</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -72448,7 +72448,7 @@
         <v>46261</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -72526,7 +72526,7 @@
         <v>46261</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -72604,7 +72604,7 @@
         <v>46217</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -72677,7 +72677,7 @@
         <v>46261</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -72755,7 +72755,7 @@
         <v>46261</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -72833,7 +72833,7 @@
         <v>44912</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -72911,7 +72911,7 @@
         <v>46217</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -72984,7 +72984,7 @@
         <v>46262</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -73062,7 +73062,7 @@
         <v>46262</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -73140,7 +73140,7 @@
         <v>46262</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -73218,7 +73218,7 @@
         <v>46262</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -73296,7 +73296,7 @@
         <v>46262</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -73374,7 +73374,7 @@
         <v>46262</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -73452,7 +73452,7 @@
         <v>44963</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -73530,7 +73530,7 @@
         <v>46262</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -73608,7 +73608,7 @@
         <v>46262</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -73686,7 +73686,7 @@
         <v>46262</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -73764,7 +73764,7 @@
         <v>44910</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -73842,7 +73842,7 @@
         <v>45117</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -73915,7 +73915,7 @@
         <v>45331</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -73993,7 +73993,7 @@
         <v>44989</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -74066,7 +74066,7 @@
         <v>45110</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -74144,7 +74144,7 @@
         <v>46269</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -74217,7 +74217,7 @@
         <v>44916</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -74290,7 +74290,7 @@
         <v>45256</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -74368,7 +74368,7 @@
         <v>46272</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -74441,7 +74441,7 @@
         <v>46272</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -74514,7 +74514,7 @@
         <v>46272</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -74587,7 +74587,7 @@
         <v>44539</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -74660,7 +74660,7 @@
         <v>44904</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -74733,7 +74733,7 @@
         <v>44904</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -74806,7 +74806,7 @@
         <v>45204</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -74879,7 +74879,7 @@
         <v>45147</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -74952,7 +74952,7 @@
         <v>46234</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -75030,7 +75030,7 @@
         <v>45040</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -75103,7 +75103,7 @@
         <v>46238</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -75176,7 +75176,7 @@
         <v>46238</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -75249,7 +75249,7 @@
         <v>46238</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -75322,7 +75322,7 @@
         <v>46238</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -75395,7 +75395,7 @@
         <v>44901</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -75468,7 +75468,7 @@
         <v>46238</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -75541,7 +75541,7 @@
         <v>45747</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -75614,7 +75614,7 @@
         <v>46238</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -75687,7 +75687,7 @@
         <v>46238</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -75760,7 +75760,7 @@
         <v>45374</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -75833,7 +75833,7 @@
         <v>45635</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -75906,7 +75906,7 @@
         <v>45301</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -75979,7 +75979,7 @@
         <v>46282</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -76052,7 +76052,7 @@
         <v>46239</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -76125,7 +76125,7 @@
         <v>45085</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -76203,7 +76203,7 @@
         <v>45104</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -76276,7 +76276,7 @@
         <v>45089</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -76349,7 +76349,7 @@
         <v>45022</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -76427,7 +76427,7 @@
         <v>44487</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -76500,7 +76500,7 @@
         <v>45755</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -76573,7 +76573,7 @@
         <v>44722</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -76646,7 +76646,7 @@
         <v>45540</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -76724,7 +76724,7 @@
         <v>44908</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -76797,7 +76797,7 @@
         <v>44867</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -76875,7 +76875,7 @@
         <v>46183</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -76948,7 +76948,7 @@
         <v>45468</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -77021,7 +77021,7 @@
         <v>45468</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -77094,7 +77094,7 @@
         <v>45236</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -77172,7 +77172,7 @@
         <v>44720</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -77245,7 +77245,7 @@
         <v>45740</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -77323,7 +77323,7 @@
         <v>45951</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -77396,7 +77396,7 @@
         <v>44589</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -77469,7 +77469,7 @@
         <v>44979</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -77542,7 +77542,7 @@
         <v>46286</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -77615,7 +77615,7 @@
         <v>46246</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -77688,7 +77688,7 @@
         <v>45625</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -77766,7 +77766,7 @@
         <v>46175</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -77839,7 +77839,7 @@
         <v>45379</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -77912,7 +77912,7 @@
         <v>44623</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -77990,7 +77990,7 @@
         <v>45196</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -78068,7 +78068,7 @@
         <v>46150</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -78141,7 +78141,7 @@
         <v>45148</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -78219,7 +78219,7 @@
         <v>45104</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -78297,7 +78297,7 @@
         <v>44973</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -78370,7 +78370,7 @@
         <v>45477</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -78443,7 +78443,7 @@
         <v>45160</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -78521,7 +78521,7 @@
         <v>44984</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -78594,7 +78594,7 @@
         <v>46209</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -78667,7 +78667,7 @@
         <v>46290</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -78745,7 +78745,7 @@
         <v>44924</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -78818,7 +78818,7 @@
         <v>46105</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -78896,7 +78896,7 @@
         <v>46035</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -78969,7 +78969,7 @@
         <v>46249</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -79047,7 +79047,7 @@
         <v>45460</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -79120,7 +79120,7 @@
         <v>45076</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -79193,7 +79193,7 @@
         <v>46290</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -79271,7 +79271,7 @@
         <v>46290</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -79349,7 +79349,7 @@
         <v>46251</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -79422,7 +79422,7 @@
         <v>46048</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -79495,7 +79495,7 @@
         <v>46295</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -79573,7 +79573,7 @@
         <v>45196</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -79651,7 +79651,7 @@
         <v>45240</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -79724,7 +79724,7 @@
         <v>44977</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -79797,7 +79797,7 @@
         <v>45258</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -79870,7 +79870,7 @@
         <v>45637</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -79943,7 +79943,7 @@
         <v>46252</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -80016,7 +80016,7 @@
         <v>45301</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -80089,7 +80089,7 @@
         <v>45301</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -80162,7 +80162,7 @@
         <v>44964</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -80235,7 +80235,7 @@
         <v>45680</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -80308,7 +80308,7 @@
         <v>46294</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -80381,7 +80381,7 @@
         <v>45321</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -80454,7 +80454,7 @@
         <v>45321</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -80532,7 +80532,7 @@
         <v>45089</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -80605,7 +80605,7 @@
         <v>45596</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -80678,7 +80678,7 @@
         <v>46217</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -80751,7 +80751,7 @@
         <v>45379</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -80824,7 +80824,7 @@
         <v>46253</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -80897,7 +80897,7 @@
         <v>44655</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -80970,7 +80970,7 @@
         <v>44984</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -81048,7 +81048,7 @@
         <v>46296</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -81121,7 +81121,7 @@
         <v>45068</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -81194,7 +81194,7 @@
         <v>44987</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -81267,7 +81267,7 @@
         <v>45988</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -81345,7 +81345,7 @@
         <v>45362</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -81418,7 +81418,7 @@
         <v>46183</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -81491,7 +81491,7 @@
         <v>46195</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -81584,7 +81584,7 @@
         <v>44564</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -81657,7 +81657,7 @@
         <v>44564</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -81730,7 +81730,7 @@
         <v>45049</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -81803,7 +81803,7 @@
         <v>45512</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -81876,7 +81876,7 @@
         <v>45512</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -81949,7 +81949,7 @@
         <v>45035</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -82022,7 +82022,7 @@
         <v>44979</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -82095,7 +82095,7 @@
         <v>45743</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -82168,7 +82168,7 @@
         <v>45216</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -82241,7 +82241,7 @@
         <v>45140</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -82314,7 +82314,7 @@
         <v>44651</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -82387,7 +82387,7 @@
         <v>45442</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -82465,7 +82465,7 @@
         <v>44785</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -82538,7 +82538,7 @@
         <v>44785</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -82611,7 +82611,7 @@
         <v>44929</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -82684,7 +82684,7 @@
         <v>44509</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -82757,7 +82757,7 @@
         <v>45740</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -82835,7 +82835,7 @@
         <v>45016</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -82908,7 +82908,7 @@
         <v>44756</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -82981,7 +82981,7 @@
         <v>45448</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -83059,7 +83059,7 @@
         <v>45671</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -83132,7 +83132,7 @@
         <v>44589</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -83210,7 +83210,7 @@
         <v>44867</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -83288,7 +83288,7 @@
         <v>44851</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -83361,7 +83361,7 @@
         <v>44783</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -83434,7 +83434,7 @@
         <v>44888</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -83507,7 +83507,7 @@
         <v>45187</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -83580,7 +83580,7 @@
         <v>44512</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -83673,7 +83673,7 @@
         <v>45610</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -83751,7 +83751,7 @@
         <v>45723</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -83824,7 +83824,7 @@
         <v>44964</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -83897,7 +83897,7 @@
         <v>45153</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -83970,7 +83970,7 @@
         <v>44672</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -84048,7 +84048,7 @@
         <v>45077</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -84121,7 +84121,7 @@
         <v>45306</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -84194,7 +84194,7 @@
         <v>45306</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -84267,7 +84267,7 @@
         <v>44946</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -84340,7 +84340,7 @@
         <v>45537</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -84418,7 +84418,7 @@
         <v>45301</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -84491,7 +84491,7 @@
         <v>45036</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -84564,7 +84564,7 @@
         <v>44904</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -84637,7 +84637,7 @@
         <v>45194</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -84715,7 +84715,7 @@
         <v>45194</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -84793,7 +84793,7 @@
         <v>45777</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -84866,7 +84866,7 @@
         <v>45551</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -84939,7 +84939,7 @@
         <v>45476</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -85012,7 +85012,7 @@
         <v>45604</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -85090,7 +85090,7 @@
         <v>45631</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -85163,7 +85163,7 @@
         <v>45525</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -85236,7 +85236,7 @@
         <v>45055</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -85314,7 +85314,7 @@
         <v>45061</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -85387,7 +85387,7 @@
         <v>45531</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -85465,7 +85465,7 @@
         <v>44783</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -85543,7 +85543,7 @@
         <v>44698</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -85616,7 +85616,7 @@
         <v>45545</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -85694,7 +85694,7 @@
         <v>45467</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -85772,7 +85772,7 @@
         <v>44711</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -85845,7 +85845,7 @@
         <v>44487</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -85923,7 +85923,7 @@
         <v>45670</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -85996,7 +85996,7 @@
         <v>45351</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -86074,7 +86074,7 @@
         <v>44671</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -86147,7 +86147,7 @@
         <v>45371</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -86225,7 +86225,7 @@
         <v>45371</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -86303,7 +86303,7 @@
         <v>45637</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -86376,7 +86376,7 @@
         <v>45525</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -86454,7 +86454,7 @@
         <v>45604</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -86527,7 +86527,7 @@
         <v>45341</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -86600,7 +86600,7 @@
         <v>45422</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -86678,7 +86678,7 @@
         <v>45587</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -86751,7 +86751,7 @@
         <v>45332</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -86824,7 +86824,7 @@
         <v>45222</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -86897,7 +86897,7 @@
         <v>44494</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -86970,7 +86970,7 @@
         <v>45785</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -87043,7 +87043,7 @@
         <v>45797</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -87116,7 +87116,7 @@
         <v>45821</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -87189,7 +87189,7 @@
         <v>45834</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -87267,7 +87267,7 @@
         <v>45848</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -87340,7 +87340,7 @@
         <v>45937</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -87418,7 +87418,7 @@
         <v>45937</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -87496,7 +87496,7 @@
         <v>45961</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -87574,7 +87574,7 @@
         <v>45961</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -87652,7 +87652,7 @@
         <v>45961</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -87730,7 +87730,7 @@
         <v>44706</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -87803,7 +87803,7 @@
         <v>46057</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -87881,7 +87881,7 @@
         <v>46085</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -87959,7 +87959,7 @@
         <v>46094</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -88037,7 +88037,7 @@
         <v>46191</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -88115,7 +88115,7 @@
         <v>46262</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -88193,7 +88193,7 @@
         <v>46262</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -88271,7 +88271,7 @@
         <v>46270</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -88344,7 +88344,7 @@
         <v>46246</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45461</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45824</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45680</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>44902</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44610</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>44896</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>45908</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44498</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>44699</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45643</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45740</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44883</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>45112</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44699</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45055</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>45936</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45877</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>45790</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45755</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45726</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45475</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>45244</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>46084</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45947</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>45531</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>45467</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45740</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45204</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>44610</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>46262</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>45530</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>45671</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>45471</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>46098</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45974</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>45505</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>45908</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>45973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>45055</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45505</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>46259</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>44497</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>45671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>45988</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>45471</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45908</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44505</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>46199</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45055</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>46154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45961</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>46073</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44868</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45638</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>46293</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45974</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45978</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>45686</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>45435</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>45467</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>45961</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>44539</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45931</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45608</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>44935</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45363</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45961</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45677</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>44904</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>46171</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45691</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45237</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45635</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>45996</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45233</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45961</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>46154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>45000</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45502</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>46086</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45938</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45961</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45971</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45985</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>44931</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>46279</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>46303</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>46308</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45604</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45615</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>44963</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45055</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45961</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>44785</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45673</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45274</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45475</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45376</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45303</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45853</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45952</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45961</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45011</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>46001</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>46174</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45699</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45722</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>45908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45985</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>46105</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45471</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45204</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45233</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45253</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>46150</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>46269</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45848</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45055</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45961</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>44931</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>44887</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45355</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45666</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45924</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>45590</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45135</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44946</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45303</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45939</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45740</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45314</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>46011</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45877</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46196</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>46084</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45266</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>46199</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45194</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45898</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46217</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>45274</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45533</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>46066</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45187</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45834</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45996</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>46290</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45180</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>44812</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45301</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45974</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44904</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>46189</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>46238</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45635</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>46197</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>46302</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45611</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45611</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>46086</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>46035</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45455</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45552</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44522</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45503</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45418</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45103</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44904</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45671</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44848</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45945</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45302</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45555</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>44935</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>44547</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44943</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45121</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44851</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>46147</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>46147</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45371</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45937</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45937</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45321</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45475</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45958</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45982</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45985</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45992</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45301</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>46174</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45740</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45740</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>45777</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45688</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>44697</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>45722</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44979</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45477</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44845</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>46105</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>46105</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>46114</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45355</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45376</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45301</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>44729</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>46209</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46098</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45244</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45201</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45140</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45238</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45089</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>46205</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45362</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46296</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>44494</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>44904</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>45530</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>45266</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45474</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>45681</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>45870</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45055</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44981</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45435</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>44699</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>45467</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45762</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45722</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45937</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>46105</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>44621</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>44825</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45740</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>44734</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>44830</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45336</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>44931</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>45468</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45359</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44944</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45782</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44908</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45931</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45831</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>44994</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45622</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45754</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>45917</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>45918</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45407</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45253</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45754</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>44935</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45958</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45961</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>45232</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45961</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45961</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45966</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45980</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44848</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45936</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45121</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45700</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>46175</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45688</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>45700</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45266</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46184</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45148</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>46184</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45740</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45152</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>45133</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>45133</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>46105</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>46105</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>46105</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44910</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -34687,7 +34687,7 @@
         <v>46126</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45068</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45985</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45677</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>45918</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45604</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45740</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45681</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>45625</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>46238</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44631</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>46240</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>44848</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44848</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>44979</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>46029</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>46044</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45740</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>45089</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>46300</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>45338</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>46266</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>46241</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45831</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>45188</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>45082</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45055</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45384</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>44981</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>44715</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45055</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45531</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>45385</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44699</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44494</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>44596</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -38607,7 +38607,7 @@
         <v>45722</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45740</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45740</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45789</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>45809</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45961</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45961</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>45961</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45965</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45966</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>46105</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>46147</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>46177</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -40020,7 +40020,7 @@
         <v>46246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -40130,7 +40130,7 @@
         <v>44683</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>44820</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44873</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>44512</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>44650</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>44582</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>44755</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44488</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>44621</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>44546</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>44851</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -40943,7 +40943,7 @@
         <v>44673</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>44851</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44504</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>44887</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>44586</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>44861</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>44588</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>44564</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>44511</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>44825</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44501</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>44565</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>44848</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>44487</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>44812</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>44545</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>44795</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>44796</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>44595</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>44565</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44756</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44867</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>44825</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -42642,7 +42642,7 @@
         <v>44571</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>44498</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>45460</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45531</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45174</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>44595</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45196</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45643</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45147</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45251</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>45525</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45012</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45033</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45021</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45278</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45260</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45722</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45642</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45211</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45211</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>44532</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>44946</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45764</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44937</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>45379</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>45191</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>44973</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45282</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45282</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45093</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>45093</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>45093</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>45237</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>45533</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>45240</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>44783</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>44901</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>44960</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45358</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45596</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45309</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45016</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>45140</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45631</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45511</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45114</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>44910</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>44904</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45567</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45256</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>44623</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>45245</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45222</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -46581,7 +46581,7 @@
         <v>44977</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>44988</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45576</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45460</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45460</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>44901</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45671</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45236</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45239</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44902</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45147</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>45160</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>45678</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45673</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45196</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45226</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45075</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45003</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45036</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45000</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>44811</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>44960</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>44785</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45671</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44573</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>44970</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         <v>45635</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45016</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45483</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>44776</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45201</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45201</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>44615</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45240</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45631</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45336</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>45035</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>45529</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>44785</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45300</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>46029</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45483</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45793</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>44532</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45159</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>45694</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45331</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45939</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>44881</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45553</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45147</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45160</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>44944</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>45117</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>45791</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>45369</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45883</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45804</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -50973,7 +50973,7 @@
         <v>45714</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>45463</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45939</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>45894</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>45159</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>44552</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>45477</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>45477</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45553</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45391</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>45201</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -51801,7 +51801,7 @@
         <v>45817</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45784</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -51947,7 +51947,7 @@
         <v>45622</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45530</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>45842</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>46099</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>44635</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45701</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>45671</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>46141</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         <v>44798</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -52619,7 +52619,7 @@
         <v>44669</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>45454</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>44847</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45622</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -52911,7 +52911,7 @@
         <v>45160</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -52989,7 +52989,7 @@
         <v>44994</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>46142</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -53140,7 +53140,7 @@
         <v>45040</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -53218,7 +53218,7 @@
         <v>45093</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>44923</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>44923</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -53437,7 +53437,7 @@
         <v>45035</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>44646</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>46147</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>46147</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>46147</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -53817,7 +53817,7 @@
         <v>46147</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -53895,7 +53895,7 @@
         <v>44912</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45621</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45301</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>46147</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -54202,7 +54202,7 @@
         <v>45272</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>44964</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>45104</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45371</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>45076</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45611</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45937</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -54728,7 +54728,7 @@
         <v>45089</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -54801,7 +54801,7 @@
         <v>45937</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45939</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -54957,7 +54957,7 @@
         <v>45489</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -55030,7 +55030,7 @@
         <v>45937</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45939</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45740</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45035</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -55337,7 +55337,7 @@
         <v>44916</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>44971</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
         <v>45947</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>45950</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45950</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45950</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>45253</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>45523</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -55926,7 +55926,7 @@
         <v>44646</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -55999,7 +55999,7 @@
         <v>45643</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -56072,7 +56072,7 @@
         <v>46120</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>45953</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45953</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45952</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45953</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45391</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>44848</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -56593,7 +56593,7 @@
         <v>44848</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45240</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -56739,7 +56739,7 @@
         <v>45302</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -56812,7 +56812,7 @@
         <v>45538</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45959</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -56963,7 +56963,7 @@
         <v>44977</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -57036,7 +57036,7 @@
         <v>45049</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -57109,7 +57109,7 @@
         <v>44979</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -57182,7 +57182,7 @@
         <v>45961</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45961</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>45961</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>44904</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45740</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -57567,7 +57567,7 @@
         <v>45740</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -57645,7 +57645,7 @@
         <v>46160</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         <v>46160</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>46160</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>46160</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -57957,7 +57957,7 @@
         <v>45535</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>46160</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>45330</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -58181,7 +58181,7 @@
         <v>45971</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>45590</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45968</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -58410,7 +58410,7 @@
         <v>45971</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>45161</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>46160</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -58639,7 +58639,7 @@
         <v>45414</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45313</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -58785,7 +58785,7 @@
         <v>45644</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>44980</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -58936,7 +58936,7 @@
         <v>45978</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -59014,7 +59014,7 @@
         <v>45215</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -59087,7 +59087,7 @@
         <v>45673</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -59160,7 +59160,7 @@
         <v>44956</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -59233,7 +59233,7 @@
         <v>45873</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45754</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45982</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>45630</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45985</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>45985</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>45604</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -59754,7 +59754,7 @@
         <v>44977</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -59827,7 +59827,7 @@
         <v>45985</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -59900,7 +59900,7 @@
         <v>45985</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -59973,7 +59973,7 @@
         <v>45985</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45215</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>44641</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45237</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -60270,7 +60270,7 @@
         <v>44820</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -60343,7 +60343,7 @@
         <v>45986</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -60421,7 +60421,7 @@
         <v>45986</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>44795</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -60572,7 +60572,7 @@
         <v>44848</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>45327</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -60723,7 +60723,7 @@
         <v>45148</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -60801,7 +60801,7 @@
         <v>45988</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -60874,7 +60874,7 @@
         <v>45343</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -60947,7 +60947,7 @@
         <v>45994</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -61020,7 +61020,7 @@
         <v>45371</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>44935</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -61166,7 +61166,7 @@
         <v>45706</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -61239,7 +61239,7 @@
         <v>45301</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -61312,7 +61312,7 @@
         <v>45301</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -61385,7 +61385,7 @@
         <v>45355</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -61458,7 +61458,7 @@
         <v>44956</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -61536,7 +61536,7 @@
         <v>45068</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -61609,7 +61609,7 @@
         <v>45160</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45478</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>46001</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -61838,7 +61838,7 @@
         <v>45140</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>46001</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -61989,7 +61989,7 @@
         <v>46001</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>46008</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -62140,7 +62140,7 @@
         <v>46008</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -62213,7 +62213,7 @@
         <v>46008</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>46008</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>46008</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -62432,7 +62432,7 @@
         <v>46008</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -62505,7 +62505,7 @@
         <v>46008</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>46008</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -62651,7 +62651,7 @@
         <v>45538</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -62724,7 +62724,7 @@
         <v>45455</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>46013</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>45265</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -62953,7 +62953,7 @@
         <v>46013</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -63031,7 +63031,7 @@
         <v>46013</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -63109,7 +63109,7 @@
         <v>46013</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -63187,7 +63187,7 @@
         <v>46013</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -63265,7 +63265,7 @@
         <v>46020</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -63338,7 +63338,7 @@
         <v>45842</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -63411,7 +63411,7 @@
         <v>45566</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -63484,7 +63484,7 @@
         <v>44728</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -63557,7 +63557,7 @@
         <v>46030</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>44939</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -63708,7 +63708,7 @@
         <v>46034</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -63781,7 +63781,7 @@
         <v>46034</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -63854,7 +63854,7 @@
         <v>46034</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -63927,7 +63927,7 @@
         <v>46034</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -64000,7 +64000,7 @@
         <v>45722</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -64073,7 +64073,7 @@
         <v>46175</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -64146,7 +64146,7 @@
         <v>44930</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -64219,7 +64219,7 @@
         <v>45589</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -64292,7 +64292,7 @@
         <v>46042</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -64365,7 +64365,7 @@
         <v>44621</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -64438,7 +64438,7 @@
         <v>46044</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>46044</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -64584,7 +64584,7 @@
         <v>46044</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -64657,7 +64657,7 @@
         <v>46044</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -64730,7 +64730,7 @@
         <v>46044</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -64803,7 +64803,7 @@
         <v>45036</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -64876,7 +64876,7 @@
         <v>46044</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -64949,7 +64949,7 @@
         <v>45272</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -65022,7 +65022,7 @@
         <v>46044</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -65095,7 +65095,7 @@
         <v>46051</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -65173,7 +65173,7 @@
         <v>45678</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -65246,7 +65246,7 @@
         <v>46055</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -65319,7 +65319,7 @@
         <v>45204</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -65392,7 +65392,7 @@
         <v>45740</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -65470,7 +65470,7 @@
         <v>45198</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -65543,7 +65543,7 @@
         <v>45390</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -65616,7 +65616,7 @@
         <v>46184</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -65694,7 +65694,7 @@
         <v>46059</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -65767,7 +65767,7 @@
         <v>45484</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -65840,7 +65840,7 @@
         <v>46184</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -65918,7 +65918,7 @@
         <v>46184</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>46184</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -66074,7 +66074,7 @@
         <v>46184</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -66152,7 +66152,7 @@
         <v>44956</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -66225,7 +66225,7 @@
         <v>45086</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -66298,7 +66298,7 @@
         <v>45261</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -66376,7 +66376,7 @@
         <v>45483</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -66449,7 +66449,7 @@
         <v>45170</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -66522,7 +66522,7 @@
         <v>45170</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -66595,7 +66595,7 @@
         <v>45121</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -66668,7 +66668,7 @@
         <v>46190</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -66741,7 +66741,7 @@
         <v>44893</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>46189</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -66887,7 +66887,7 @@
         <v>44942</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -66960,7 +66960,7 @@
         <v>45148</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>44973</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -67111,7 +67111,7 @@
         <v>45916</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -67184,7 +67184,7 @@
         <v>44861</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -67257,7 +67257,7 @@
         <v>45245</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -67335,7 +67335,7 @@
         <v>44973</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -67408,7 +67408,7 @@
         <v>45202</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -67481,7 +67481,7 @@
         <v>45133</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -67554,7 +67554,7 @@
         <v>46197</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -67627,7 +67627,7 @@
         <v>44977</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -67700,7 +67700,7 @@
         <v>46195</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -67773,7 +67773,7 @@
         <v>46195</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -67846,7 +67846,7 @@
         <v>45366</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -67924,7 +67924,7 @@
         <v>45566</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -67997,7 +67997,7 @@
         <v>44912</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -68075,7 +68075,7 @@
         <v>46197</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -68148,7 +68148,7 @@
         <v>44963</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -68226,7 +68226,7 @@
         <v>46113</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -68299,7 +68299,7 @@
         <v>46113</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -68377,7 +68377,7 @@
         <v>46113</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -68450,7 +68450,7 @@
         <v>46199</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -68528,7 +68528,7 @@
         <v>45117</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -68601,7 +68601,7 @@
         <v>46199</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -68679,7 +68679,7 @@
         <v>45331</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -68757,7 +68757,7 @@
         <v>44989</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -68830,7 +68830,7 @@
         <v>45110</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -68908,7 +68908,7 @@
         <v>46202</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -68981,7 +68981,7 @@
         <v>44916</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -69054,7 +69054,7 @@
         <v>45256</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -69132,7 +69132,7 @@
         <v>46128</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -69205,7 +69205,7 @@
         <v>46132</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -69283,7 +69283,7 @@
         <v>46132</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -69361,7 +69361,7 @@
         <v>44539</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -69434,7 +69434,7 @@
         <v>44904</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -69507,7 +69507,7 @@
         <v>44904</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -69580,7 +69580,7 @@
         <v>45204</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -69653,7 +69653,7 @@
         <v>45147</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -69726,7 +69726,7 @@
         <v>45945</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -69804,7 +69804,7 @@
         <v>45040</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -69877,7 +69877,7 @@
         <v>44901</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -69950,7 +69950,7 @@
         <v>45754</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -70028,7 +70028,7 @@
         <v>45818</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -70101,7 +70101,7 @@
         <v>45931</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -70174,7 +70174,7 @@
         <v>45374</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -70247,7 +70247,7 @@
         <v>45635</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -70320,7 +70320,7 @@
         <v>44748</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -70398,7 +70398,7 @@
         <v>45301</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -70471,7 +70471,7 @@
         <v>46205</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -70544,7 +70544,7 @@
         <v>46205</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -70622,7 +70622,7 @@
         <v>45945</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -70695,7 +70695,7 @@
         <v>46205</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -70768,7 +70768,7 @@
         <v>45085</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -70846,7 +70846,7 @@
         <v>46029</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -70919,7 +70919,7 @@
         <v>45477</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -70997,7 +70997,7 @@
         <v>45104</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -71070,7 +71070,7 @@
         <v>45089</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -71143,7 +71143,7 @@
         <v>45022</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -71221,7 +71221,7 @@
         <v>44487</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -71294,7 +71294,7 @@
         <v>45755</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -71367,7 +71367,7 @@
         <v>44722</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -71440,7 +71440,7 @@
         <v>45540</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -71518,7 +71518,7 @@
         <v>44908</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -71591,7 +71591,7 @@
         <v>44867</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -71669,7 +71669,7 @@
         <v>45468</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -71742,7 +71742,7 @@
         <v>45468</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -71815,7 +71815,7 @@
         <v>45236</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -71893,7 +71893,7 @@
         <v>44720</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -71966,7 +71966,7 @@
         <v>46217</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>45740</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -72117,7 +72117,7 @@
         <v>44589</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -72190,7 +72190,7 @@
         <v>46217</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -72263,7 +72263,7 @@
         <v>44979</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -72336,7 +72336,7 @@
         <v>46217</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -72409,7 +72409,7 @@
         <v>45625</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -72487,7 +72487,7 @@
         <v>45379</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -72560,7 +72560,7 @@
         <v>44623</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -72638,7 +72638,7 @@
         <v>45196</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -72716,7 +72716,7 @@
         <v>46272</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -72789,7 +72789,7 @@
         <v>46272</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -72862,7 +72862,7 @@
         <v>46272</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -72935,7 +72935,7 @@
         <v>45148</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -73013,7 +73013,7 @@
         <v>45104</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -73091,7 +73091,7 @@
         <v>44973</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -73164,7 +73164,7 @@
         <v>45477</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -73237,7 +73237,7 @@
         <v>45160</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -73315,7 +73315,7 @@
         <v>44984</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -73388,7 +73388,7 @@
         <v>44924</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -73461,7 +73461,7 @@
         <v>45460</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -73534,7 +73534,7 @@
         <v>45076</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -73607,7 +73607,7 @@
         <v>46234</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -73685,7 +73685,7 @@
         <v>45196</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -73763,7 +73763,7 @@
         <v>45240</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -73836,7 +73836,7 @@
         <v>44977</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -73909,7 +73909,7 @@
         <v>45258</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -73982,7 +73982,7 @@
         <v>45637</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -74055,7 +74055,7 @@
         <v>45301</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -74128,7 +74128,7 @@
         <v>45301</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -74201,7 +74201,7 @@
         <v>46238</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -74274,7 +74274,7 @@
         <v>46238</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -74347,7 +74347,7 @@
         <v>44964</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -74420,7 +74420,7 @@
         <v>45680</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -74493,7 +74493,7 @@
         <v>45321</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -74566,7 +74566,7 @@
         <v>45321</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -74644,7 +74644,7 @@
         <v>46238</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -74717,7 +74717,7 @@
         <v>46238</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -74790,7 +74790,7 @@
         <v>46238</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -74863,7 +74863,7 @@
         <v>45089</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -74936,7 +74936,7 @@
         <v>46238</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -75009,7 +75009,7 @@
         <v>46238</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -75082,7 +75082,7 @@
         <v>45596</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -75155,7 +75155,7 @@
         <v>46282</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -75228,7 +75228,7 @@
         <v>46239</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -75301,7 +75301,7 @@
         <v>45379</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -75374,7 +75374,7 @@
         <v>44655</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -75447,7 +75447,7 @@
         <v>44984</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -75525,7 +75525,7 @@
         <v>45068</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -75598,7 +75598,7 @@
         <v>44987</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -75671,7 +75671,7 @@
         <v>46183</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -75744,7 +75744,7 @@
         <v>44564</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -75817,7 +75817,7 @@
         <v>44564</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -75890,7 +75890,7 @@
         <v>45049</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -75963,7 +75963,7 @@
         <v>45512</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -76036,7 +76036,7 @@
         <v>45512</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -76109,7 +76109,7 @@
         <v>45035</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -76182,7 +76182,7 @@
         <v>44979</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -76255,7 +76255,7 @@
         <v>45951</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -76328,7 +76328,7 @@
         <v>45743</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -76401,7 +76401,7 @@
         <v>46286</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -76474,7 +76474,7 @@
         <v>45216</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -76547,7 +76547,7 @@
         <v>45140</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -76620,7 +76620,7 @@
         <v>44651</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -76693,7 +76693,7 @@
         <v>45442</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -76771,7 +76771,7 @@
         <v>44785</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -76844,7 +76844,7 @@
         <v>46246</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -76917,7 +76917,7 @@
         <v>44785</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -76990,7 +76990,7 @@
         <v>46175</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -77063,7 +77063,7 @@
         <v>44929</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -77136,7 +77136,7 @@
         <v>44509</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -77209,7 +77209,7 @@
         <v>46150</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -77282,7 +77282,7 @@
         <v>45740</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -77360,7 +77360,7 @@
         <v>45016</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -77433,7 +77433,7 @@
         <v>44756</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -77506,7 +77506,7 @@
         <v>45448</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -77584,7 +77584,7 @@
         <v>46209</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -77657,7 +77657,7 @@
         <v>45671</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -77730,7 +77730,7 @@
         <v>44589</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -77808,7 +77808,7 @@
         <v>46290</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -77886,7 +77886,7 @@
         <v>44867</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -77964,7 +77964,7 @@
         <v>46105</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -78042,7 +78042,7 @@
         <v>46035</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -78115,7 +78115,7 @@
         <v>44851</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -78188,7 +78188,7 @@
         <v>46249</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -78266,7 +78266,7 @@
         <v>44783</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -78339,7 +78339,7 @@
         <v>46290</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -78417,7 +78417,7 @@
         <v>46290</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -78495,7 +78495,7 @@
         <v>44888</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -78568,7 +78568,7 @@
         <v>46251</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -78641,7 +78641,7 @@
         <v>46048</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -78714,7 +78714,7 @@
         <v>45187</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -78787,7 +78787,7 @@
         <v>44512</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -78880,7 +78880,7 @@
         <v>46295</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -78958,7 +78958,7 @@
         <v>45610</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -79036,7 +79036,7 @@
         <v>45723</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -79109,7 +79109,7 @@
         <v>44964</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -79182,7 +79182,7 @@
         <v>46252</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -79255,7 +79255,7 @@
         <v>45153</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -79328,7 +79328,7 @@
         <v>44672</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -79406,7 +79406,7 @@
         <v>46294</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -79479,7 +79479,7 @@
         <v>45077</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -79552,7 +79552,7 @@
         <v>45306</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -79625,7 +79625,7 @@
         <v>45306</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -79698,7 +79698,7 @@
         <v>44946</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -79771,7 +79771,7 @@
         <v>45537</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -79849,7 +79849,7 @@
         <v>46217</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -79922,7 +79922,7 @@
         <v>46253</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -79995,7 +79995,7 @@
         <v>45301</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -80068,7 +80068,7 @@
         <v>46296</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -80141,7 +80141,7 @@
         <v>45988</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -80219,7 +80219,7 @@
         <v>45362</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -80292,7 +80292,7 @@
         <v>46183</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -80365,7 +80365,7 @@
         <v>46195</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -80458,7 +80458,7 @@
         <v>45036</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -80531,7 +80531,7 @@
         <v>46300</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -80609,7 +80609,7 @@
         <v>44904</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -80682,7 +80682,7 @@
         <v>46301</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -80760,7 +80760,7 @@
         <v>45194</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -80838,7 +80838,7 @@
         <v>45194</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -80916,7 +80916,7 @@
         <v>46300</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -80994,7 +80994,7 @@
         <v>45777</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -81067,7 +81067,7 @@
         <v>45551</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -81140,7 +81140,7 @@
         <v>46300</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -81218,7 +81218,7 @@
         <v>46300</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -81296,7 +81296,7 @@
         <v>46300</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -81374,7 +81374,7 @@
         <v>46301</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -81447,7 +81447,7 @@
         <v>46300</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -81525,7 +81525,7 @@
         <v>46300</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -81603,7 +81603,7 @@
         <v>45476</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -81676,7 +81676,7 @@
         <v>45604</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -81754,7 +81754,7 @@
         <v>45625</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -81832,7 +81832,7 @@
         <v>46189</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -81905,7 +81905,7 @@
         <v>46259</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -81983,7 +81983,7 @@
         <v>46303</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -82056,7 +82056,7 @@
         <v>45793</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -82134,7 +82134,7 @@
         <v>46262</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -82212,7 +82212,7 @@
         <v>46262</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -82290,7 +82290,7 @@
         <v>46262</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -82368,7 +82368,7 @@
         <v>46262</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -82446,7 +82446,7 @@
         <v>45790</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -82519,7 +82519,7 @@
         <v>46261</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -82597,7 +82597,7 @@
         <v>46261</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -82675,7 +82675,7 @@
         <v>46262</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -82753,7 +82753,7 @@
         <v>46261</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -82831,7 +82831,7 @@
         <v>45749</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -82904,7 +82904,7 @@
         <v>46261</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -82982,7 +82982,7 @@
         <v>45561</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -83060,7 +83060,7 @@
         <v>46261</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -83138,7 +83138,7 @@
         <v>46261</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -83216,7 +83216,7 @@
         <v>45799</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -83289,7 +83289,7 @@
         <v>46262</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -83367,7 +83367,7 @@
         <v>46262</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -83445,7 +83445,7 @@
         <v>46262</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -83523,7 +83523,7 @@
         <v>45706</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -83596,7 +83596,7 @@
         <v>45393</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -83669,7 +83669,7 @@
         <v>45287</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -83747,7 +83747,7 @@
         <v>46262</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -83825,7 +83825,7 @@
         <v>46261</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -83903,7 +83903,7 @@
         <v>44956</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -83976,7 +83976,7 @@
         <v>45807</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -84049,7 +84049,7 @@
         <v>46308</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -84122,7 +84122,7 @@
         <v>45810</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -84195,7 +84195,7 @@
         <v>46310</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -84268,7 +84268,7 @@
         <v>45813</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -84341,7 +84341,7 @@
         <v>46310</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -84419,7 +84419,7 @@
         <v>46269</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -84492,7 +84492,7 @@
         <v>45819</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -84565,7 +84565,7 @@
         <v>45825</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -84638,7 +84638,7 @@
         <v>45831</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -84711,7 +84711,7 @@
         <v>45831</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -84784,7 +84784,7 @@
         <v>45793</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -84857,7 +84857,7 @@
         <v>45838</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -84930,7 +84930,7 @@
         <v>45838</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -85003,7 +85003,7 @@
         <v>45790</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -85076,7 +85076,7 @@
         <v>45847</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -85149,7 +85149,7 @@
         <v>45848</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -85222,7 +85222,7 @@
         <v>45849</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -85295,7 +85295,7 @@
         <v>45817</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -85368,7 +85368,7 @@
         <v>45719</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -85441,7 +85441,7 @@
         <v>45853</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -85514,7 +85514,7 @@
         <v>45783</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -85587,7 +85587,7 @@
         <v>44977</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -85660,7 +85660,7 @@
         <v>45775</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -85733,7 +85733,7 @@
         <v>45877</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -85806,7 +85806,7 @@
         <v>45631</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -85879,7 +85879,7 @@
         <v>45525</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -85952,7 +85952,7 @@
         <v>45055</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -86030,7 +86030,7 @@
         <v>45061</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -86103,7 +86103,7 @@
         <v>45531</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -86181,7 +86181,7 @@
         <v>44783</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -86259,7 +86259,7 @@
         <v>44698</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -86332,7 +86332,7 @@
         <v>45545</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -86410,7 +86410,7 @@
         <v>45467</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -86488,7 +86488,7 @@
         <v>44711</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -86561,7 +86561,7 @@
         <v>44487</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -86639,7 +86639,7 @@
         <v>45670</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -86712,7 +86712,7 @@
         <v>45351</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -86790,7 +86790,7 @@
         <v>44671</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -86863,7 +86863,7 @@
         <v>45371</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -86941,7 +86941,7 @@
         <v>45371</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -87019,7 +87019,7 @@
         <v>45637</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -87092,7 +87092,7 @@
         <v>45525</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -87170,7 +87170,7 @@
         <v>45604</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -87243,7 +87243,7 @@
         <v>45341</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -87316,7 +87316,7 @@
         <v>45422</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -87394,7 +87394,7 @@
         <v>45587</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -87467,7 +87467,7 @@
         <v>45332</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -87540,7 +87540,7 @@
         <v>45222</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -87613,7 +87613,7 @@
         <v>44494</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -87686,7 +87686,7 @@
         <v>45785</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -87759,7 +87759,7 @@
         <v>45797</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -87832,7 +87832,7 @@
         <v>45821</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -87905,7 +87905,7 @@
         <v>45834</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -87983,7 +87983,7 @@
         <v>45848</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -88056,7 +88056,7 @@
         <v>45937</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -88134,7 +88134,7 @@
         <v>45937</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -88212,7 +88212,7 @@
         <v>45961</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -88290,7 +88290,7 @@
         <v>45961</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -88368,7 +88368,7 @@
         <v>45961</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -88446,7 +88446,7 @@
         <v>44706</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -88519,7 +88519,7 @@
         <v>46057</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -88597,7 +88597,7 @@
         <v>46085</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -88675,7 +88675,7 @@
         <v>46094</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -88753,7 +88753,7 @@
         <v>46191</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -88831,7 +88831,7 @@
         <v>46270</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -88904,7 +88904,7 @@
         <v>46246</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -88982,7 +88982,7 @@
         <v>46303</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -89055,7 +89055,7 @@
         <v>46262</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -89133,7 +89133,7 @@
         <v>46262</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45461</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45824</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45680</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>44902</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44610</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>44896</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>45908</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44498</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>44699</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45643</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45740</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44883</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>45112</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44699</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45055</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>45936</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45877</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>44487</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>45790</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45755</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45726</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44896</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45475</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>45244</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>46084</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45947</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>45531</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>45467</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45740</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45204</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>44610</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>45740</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>46262</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>45530</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>45671</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>45471</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>46098</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45974</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>45505</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>45908</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>45973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>45055</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45505</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>46259</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>44497</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>45671</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>45988</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>45471</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45908</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44505</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>46199</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45055</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>46154</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45961</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>46073</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44868</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45638</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>46293</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45974</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45978</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>45686</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>45435</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>45467</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>45961</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>44539</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45931</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45608</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>44935</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45363</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45961</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45677</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>44904</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>46171</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45691</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45237</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45635</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>45996</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45233</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45961</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>46154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>45000</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45502</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>46086</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45938</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45961</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45971</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45985</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>44931</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>46279</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>46303</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>46308</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45604</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45615</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>44963</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45055</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45961</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>44785</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45673</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45274</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45475</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45376</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45303</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45853</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45952</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45961</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45011</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>46001</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>46174</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45699</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45722</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>45908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45985</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>46105</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45471</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45204</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45233</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45253</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>46150</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>46269</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45848</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45055</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45961</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>44931</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>44887</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45355</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45666</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45924</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>45590</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45135</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44946</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45303</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45939</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45740</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45314</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>46011</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45877</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46196</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>46084</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45266</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>46199</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45194</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45898</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46217</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>45274</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45533</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>46066</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45187</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45834</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45996</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>46290</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45180</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>44812</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45301</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45974</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44904</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>46189</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>46238</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45635</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>46197</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>46302</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45611</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45611</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>46086</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>46035</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45455</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45552</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44522</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45503</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45418</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45103</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44904</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45671</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44848</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45945</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45302</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45555</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>44935</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>44547</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44943</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45121</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44851</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>46147</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>46147</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45371</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45937</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45937</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45321</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45475</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45958</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45982</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45985</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45992</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45301</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>46174</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45740</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45740</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>45777</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45688</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>44697</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>45722</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44979</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45477</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44845</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>46105</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>46105</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>46114</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45355</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45376</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45301</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>44729</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>46209</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46098</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45244</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45201</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45140</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45238</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45089</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>46205</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45362</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46296</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>44494</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>44904</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>45530</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>45266</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45474</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>45681</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>45870</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45055</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44981</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45435</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>44699</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>45467</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45762</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45722</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45937</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>46105</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>44621</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>44825</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45740</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>44734</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>44830</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45336</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>44931</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>45468</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45359</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44944</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45782</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44908</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45931</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45831</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>44994</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45622</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45754</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>45917</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>45918</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45407</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45253</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45754</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>44935</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45958</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45961</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>45232</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45961</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45961</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45966</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45980</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44848</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45936</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45121</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45700</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>46175</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45688</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>45700</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45266</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46184</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45148</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>46184</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45740</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45152</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>45133</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>45133</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>46105</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>46105</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>46105</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44910</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -34687,7 +34687,7 @@
         <v>46126</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45068</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45985</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45677</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>45918</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45604</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45740</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45681</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>45625</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>46238</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44631</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>46240</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>44848</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44848</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>44979</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>46029</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>46044</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45740</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>45089</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>46300</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>45338</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>46266</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>46241</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45831</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>45188</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>45082</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45055</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45384</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>44981</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>44715</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45055</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45531</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>45385</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44699</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44494</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>44596</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -38607,7 +38607,7 @@
         <v>45722</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45740</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45740</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45789</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>45809</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45961</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45961</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>45961</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45965</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45966</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>46105</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>46147</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>46177</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -40020,7 +40020,7 @@
         <v>46246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -40130,7 +40130,7 @@
         <v>44683</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>44820</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44873</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>44512</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>44650</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>44582</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>44755</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44488</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>44621</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>44546</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>44851</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -40943,7 +40943,7 @@
         <v>44673</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>44851</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44504</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>44887</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>44586</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>44861</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>44588</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>44564</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>44511</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>44825</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44501</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>44565</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>44848</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>44487</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>44812</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>44545</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>44795</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>44796</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>44595</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>44565</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44756</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44867</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>44825</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -42642,7 +42642,7 @@
         <v>44571</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>44498</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>45460</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45531</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45174</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>44595</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45196</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45643</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45147</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45251</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>45525</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45012</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45033</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45021</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45278</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45260</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45722</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45642</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45211</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45211</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>44532</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>44946</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45764</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44937</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>45379</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>45191</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>44973</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45282</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45282</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45093</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>45093</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>45093</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>45237</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>45533</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>45240</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>44783</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>44901</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>44960</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45358</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45596</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45309</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45016</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>45140</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45631</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45511</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45114</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>44910</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>44904</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45567</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45256</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>44623</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>45245</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45222</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -46581,7 +46581,7 @@
         <v>44977</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>44988</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45576</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45460</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45460</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>44901</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45671</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45236</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45239</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>44902</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45147</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>45160</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>45678</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45673</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45196</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45226</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45075</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45003</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45036</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45000</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>44811</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>44960</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>44785</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45671</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>44573</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>44970</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         <v>45635</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45016</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45483</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>44776</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45201</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45201</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>44615</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45240</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45631</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45336</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>45035</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>45529</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>44785</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45300</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>46029</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45483</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45793</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>44532</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45159</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>45694</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45331</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45939</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>44881</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45553</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45147</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45160</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>44944</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>45117</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>45791</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>45369</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45883</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45804</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -50973,7 +50973,7 @@
         <v>45714</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>45463</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45939</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>45894</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>45159</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>44552</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>45477</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>45477</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45553</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45391</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>45201</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -51801,7 +51801,7 @@
         <v>45817</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45784</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -51947,7 +51947,7 @@
         <v>45622</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45530</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>45842</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>46099</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>44635</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45701</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>45671</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>46141</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         <v>44798</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -52619,7 +52619,7 @@
         <v>44669</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>45454</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>44847</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45622</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -52911,7 +52911,7 @@
         <v>45160</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -52989,7 +52989,7 @@
         <v>44994</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>46142</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -53140,7 +53140,7 @@
         <v>45040</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -53218,7 +53218,7 @@
         <v>45093</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>44923</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>44923</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -53437,7 +53437,7 @@
         <v>45035</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>44646</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>46147</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>46147</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>46147</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -53817,7 +53817,7 @@
         <v>46147</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -53895,7 +53895,7 @@
         <v>44912</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45621</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45301</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>46147</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -54202,7 +54202,7 @@
         <v>45272</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>44964</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -54353,7 +54353,7 @@
         <v>45104</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45371</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>45076</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>45611</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45937</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -54728,7 +54728,7 @@
         <v>45089</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -54801,7 +54801,7 @@
         <v>45937</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45939</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -54957,7 +54957,7 @@
         <v>45489</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -55030,7 +55030,7 @@
         <v>45937</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45939</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45740</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45035</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -55337,7 +55337,7 @@
         <v>44916</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>44971</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
         <v>45947</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>45950</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45950</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45950</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>45253</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>45523</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -55926,7 +55926,7 @@
         <v>44646</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -55999,7 +55999,7 @@
         <v>45643</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -56072,7 +56072,7 @@
         <v>46120</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>45953</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45953</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45952</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45953</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45391</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>44848</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -56593,7 +56593,7 @@
         <v>44848</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45240</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -56739,7 +56739,7 @@
         <v>45302</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -56812,7 +56812,7 @@
         <v>45538</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45959</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -56963,7 +56963,7 @@
         <v>44977</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -57036,7 +57036,7 @@
         <v>45049</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -57109,7 +57109,7 @@
         <v>44979</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -57182,7 +57182,7 @@
         <v>45961</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45961</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>45961</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>44904</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45740</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -57567,7 +57567,7 @@
         <v>45740</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -57645,7 +57645,7 @@
         <v>46160</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         <v>46160</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>46160</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>46160</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -57957,7 +57957,7 @@
         <v>45535</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>46160</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>45330</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -58181,7 +58181,7 @@
         <v>45971</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>45590</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45968</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -58410,7 +58410,7 @@
         <v>45971</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>45161</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>46160</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -58639,7 +58639,7 @@
         <v>45414</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45313</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -58785,7 +58785,7 @@
         <v>45644</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>44980</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -58936,7 +58936,7 @@
         <v>45978</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -59014,7 +59014,7 @@
         <v>45215</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -59087,7 +59087,7 @@
         <v>45673</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -59160,7 +59160,7 @@
         <v>44956</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -59233,7 +59233,7 @@
         <v>45873</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45754</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45982</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>45630</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45985</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>45985</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>45604</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -59754,7 +59754,7 @@
         <v>44977</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -59827,7 +59827,7 @@
         <v>45985</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -59900,7 +59900,7 @@
         <v>45985</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -59973,7 +59973,7 @@
         <v>45985</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>45215</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>44641</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -60197,7 +60197,7 @@
         <v>45237</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -60270,7 +60270,7 @@
         <v>44820</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -60343,7 +60343,7 @@
         <v>45986</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -60421,7 +60421,7 @@
         <v>45986</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>44795</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -60572,7 +60572,7 @@
         <v>44848</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>45327</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -60723,7 +60723,7 @@
         <v>45148</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -60801,7 +60801,7 @@
         <v>45988</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -60874,7 +60874,7 @@
         <v>45343</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -60947,7 +60947,7 @@
         <v>45994</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -61020,7 +61020,7 @@
         <v>45371</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>44935</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -61166,7 +61166,7 @@
         <v>45706</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -61239,7 +61239,7 @@
         <v>45301</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -61312,7 +61312,7 @@
         <v>45301</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -61385,7 +61385,7 @@
         <v>45355</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -61458,7 +61458,7 @@
         <v>44956</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -61536,7 +61536,7 @@
         <v>45068</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -61609,7 +61609,7 @@
         <v>45160</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45478</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>46001</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -61838,7 +61838,7 @@
         <v>45140</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>46001</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -61989,7 +61989,7 @@
         <v>46001</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>46008</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -62140,7 +62140,7 @@
         <v>46008</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -62213,7 +62213,7 @@
         <v>46008</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>46008</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>46008</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -62432,7 +62432,7 @@
         <v>46008</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -62505,7 +62505,7 @@
         <v>46008</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>46008</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -62651,7 +62651,7 @@
         <v>45538</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -62724,7 +62724,7 @@
         <v>45455</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>46013</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>45265</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -62953,7 +62953,7 @@
         <v>46013</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -63031,7 +63031,7 @@
         <v>46013</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -63109,7 +63109,7 @@
         <v>46013</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -63187,7 +63187,7 @@
         <v>46013</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -63265,7 +63265,7 @@
         <v>46020</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -63338,7 +63338,7 @@
         <v>45842</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -63411,7 +63411,7 @@
         <v>45566</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -63484,7 +63484,7 @@
         <v>44728</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -63557,7 +63557,7 @@
         <v>46030</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>44939</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -63708,7 +63708,7 @@
         <v>46034</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -63781,7 +63781,7 @@
         <v>46034</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -63854,7 +63854,7 @@
         <v>46034</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -63927,7 +63927,7 @@
         <v>46034</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -64000,7 +64000,7 @@
         <v>45722</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -64073,7 +64073,7 @@
         <v>46175</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -64146,7 +64146,7 @@
         <v>44930</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -64219,7 +64219,7 @@
         <v>45589</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -64292,7 +64292,7 @@
         <v>46042</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -64365,7 +64365,7 @@
         <v>44621</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -64438,7 +64438,7 @@
         <v>46044</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>46044</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -64584,7 +64584,7 @@
         <v>46044</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -64657,7 +64657,7 @@
         <v>46044</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -64730,7 +64730,7 @@
         <v>46044</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -64803,7 +64803,7 @@
         <v>45036</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -64876,7 +64876,7 @@
         <v>46044</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -64949,7 +64949,7 @@
         <v>45272</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -65022,7 +65022,7 @@
         <v>46044</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -65095,7 +65095,7 @@
         <v>46051</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -65173,7 +65173,7 @@
         <v>45678</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -65246,7 +65246,7 @@
         <v>46055</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -65319,7 +65319,7 @@
         <v>45204</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -65392,7 +65392,7 @@
         <v>45740</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -65470,7 +65470,7 @@
         <v>45198</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -65543,7 +65543,7 @@
         <v>45390</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -65616,7 +65616,7 @@
         <v>46184</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -65694,7 +65694,7 @@
         <v>46059</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -65767,7 +65767,7 @@
         <v>45484</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -65840,7 +65840,7 @@
         <v>46184</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -65918,7 +65918,7 @@
         <v>46184</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>46184</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -66074,7 +66074,7 @@
         <v>46184</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -66152,7 +66152,7 @@
         <v>44956</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -66225,7 +66225,7 @@
         <v>45086</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -66298,7 +66298,7 @@
         <v>45261</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -66376,7 +66376,7 @@
         <v>45483</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -66449,7 +66449,7 @@
         <v>45170</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -66522,7 +66522,7 @@
         <v>45170</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -66595,7 +66595,7 @@
         <v>45121</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -66668,7 +66668,7 @@
         <v>46190</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -66741,7 +66741,7 @@
         <v>44893</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>46189</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -66887,7 +66887,7 @@
         <v>44942</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -66960,7 +66960,7 @@
         <v>45148</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>44973</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -67111,7 +67111,7 @@
         <v>45916</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -67184,7 +67184,7 @@
         <v>44861</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -67257,7 +67257,7 @@
         <v>45245</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -67335,7 +67335,7 @@
         <v>44973</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -67408,7 +67408,7 @@
         <v>45202</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -67481,7 +67481,7 @@
         <v>45133</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -67554,7 +67554,7 @@
         <v>46197</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -67627,7 +67627,7 @@
         <v>44977</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -67700,7 +67700,7 @@
         <v>46195</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -67773,7 +67773,7 @@
         <v>46195</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -67846,7 +67846,7 @@
         <v>45366</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -67924,7 +67924,7 @@
         <v>45566</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -67997,7 +67997,7 @@
         <v>44912</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -68075,7 +68075,7 @@
         <v>46197</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -68148,7 +68148,7 @@
         <v>44963</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -68226,7 +68226,7 @@
         <v>46113</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -68299,7 +68299,7 @@
         <v>46113</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -68377,7 +68377,7 @@
         <v>46113</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -68450,7 +68450,7 @@
         <v>46199</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -68528,7 +68528,7 @@
         <v>45117</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -68601,7 +68601,7 @@
         <v>46199</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -68679,7 +68679,7 @@
         <v>45331</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -68757,7 +68757,7 @@
         <v>44989</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -68830,7 +68830,7 @@
         <v>45110</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -68908,7 +68908,7 @@
         <v>46202</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -68981,7 +68981,7 @@
         <v>44916</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -69054,7 +69054,7 @@
         <v>45256</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -69132,7 +69132,7 @@
         <v>46128</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -69205,7 +69205,7 @@
         <v>46132</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -69283,7 +69283,7 @@
         <v>46132</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -69361,7 +69361,7 @@
         <v>44539</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -69434,7 +69434,7 @@
         <v>44904</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -69507,7 +69507,7 @@
         <v>44904</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -69580,7 +69580,7 @@
         <v>45204</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -69653,7 +69653,7 @@
         <v>45147</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -69726,7 +69726,7 @@
         <v>45945</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -69804,7 +69804,7 @@
         <v>45040</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -69877,7 +69877,7 @@
         <v>44901</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -69950,7 +69950,7 @@
         <v>45754</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -70028,7 +70028,7 @@
         <v>45818</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -70101,7 +70101,7 @@
         <v>45931</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -70174,7 +70174,7 @@
         <v>45374</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -70247,7 +70247,7 @@
         <v>45635</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -70320,7 +70320,7 @@
         <v>44748</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -70398,7 +70398,7 @@
         <v>45301</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -70471,7 +70471,7 @@
         <v>46205</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -70544,7 +70544,7 @@
         <v>46205</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -70622,7 +70622,7 @@
         <v>45945</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -70695,7 +70695,7 @@
         <v>46205</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -70768,7 +70768,7 @@
         <v>45085</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -70846,7 +70846,7 @@
         <v>46029</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -70919,7 +70919,7 @@
         <v>45477</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -70997,7 +70997,7 @@
         <v>45104</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -71070,7 +71070,7 @@
         <v>45089</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -71143,7 +71143,7 @@
         <v>45022</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -71221,7 +71221,7 @@
         <v>44487</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -71294,7 +71294,7 @@
         <v>45755</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -71367,7 +71367,7 @@
         <v>44722</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -71440,7 +71440,7 @@
         <v>45540</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -71518,7 +71518,7 @@
         <v>44908</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -71591,7 +71591,7 @@
         <v>44867</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -71669,7 +71669,7 @@
         <v>45468</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -71742,7 +71742,7 @@
         <v>45468</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -71815,7 +71815,7 @@
         <v>45236</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -71893,7 +71893,7 @@
         <v>44720</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -71966,7 +71966,7 @@
         <v>46217</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>45740</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -72117,7 +72117,7 @@
         <v>44589</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -72190,7 +72190,7 @@
         <v>46217</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -72263,7 +72263,7 @@
         <v>44979</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -72336,7 +72336,7 @@
         <v>46217</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -72409,7 +72409,7 @@
         <v>45625</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -72487,7 +72487,7 @@
         <v>45379</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -72560,7 +72560,7 @@
         <v>44623</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -72638,7 +72638,7 @@
         <v>45196</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -72716,7 +72716,7 @@
         <v>46272</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -72789,7 +72789,7 @@
         <v>46272</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -72862,7 +72862,7 @@
         <v>46272</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -72935,7 +72935,7 @@
         <v>45148</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -73013,7 +73013,7 @@
         <v>45104</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -73091,7 +73091,7 @@
         <v>44973</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -73164,7 +73164,7 @@
         <v>45477</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -73237,7 +73237,7 @@
         <v>45160</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -73315,7 +73315,7 @@
         <v>44984</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -73388,7 +73388,7 @@
         <v>44924</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -73461,7 +73461,7 @@
         <v>45460</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -73534,7 +73534,7 @@
         <v>45076</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -73607,7 +73607,7 @@
         <v>46234</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -73685,7 +73685,7 @@
         <v>45196</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -73763,7 +73763,7 @@
         <v>45240</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -73836,7 +73836,7 @@
         <v>44977</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -73909,7 +73909,7 @@
         <v>45258</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -73982,7 +73982,7 @@
         <v>45637</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -74055,7 +74055,7 @@
         <v>45301</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -74128,7 +74128,7 @@
         <v>45301</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -74201,7 +74201,7 @@
         <v>46238</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -74274,7 +74274,7 @@
         <v>46238</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -74347,7 +74347,7 @@
         <v>44964</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -74420,7 +74420,7 @@
         <v>45680</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -74493,7 +74493,7 @@
         <v>45321</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -74566,7 +74566,7 @@
         <v>45321</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -74644,7 +74644,7 @@
         <v>46238</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -74717,7 +74717,7 @@
         <v>46238</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -74790,7 +74790,7 @@
         <v>46238</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -74863,7 +74863,7 @@
         <v>45089</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -74936,7 +74936,7 @@
         <v>46238</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -75009,7 +75009,7 @@
         <v>46238</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -75082,7 +75082,7 @@
         <v>45596</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -75155,7 +75155,7 @@
         <v>46282</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -75228,7 +75228,7 @@
         <v>46239</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -75301,7 +75301,7 @@
         <v>45379</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -75374,7 +75374,7 @@
         <v>44655</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -75447,7 +75447,7 @@
         <v>44984</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -75525,7 +75525,7 @@
         <v>45068</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -75598,7 +75598,7 @@
         <v>44987</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -75671,7 +75671,7 @@
         <v>46183</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -75744,7 +75744,7 @@
         <v>44564</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -75817,7 +75817,7 @@
         <v>44564</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -75890,7 +75890,7 @@
         <v>45049</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -75963,7 +75963,7 @@
         <v>45512</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -76036,7 +76036,7 @@
         <v>45512</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -76109,7 +76109,7 @@
         <v>45035</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -76182,7 +76182,7 @@
         <v>44979</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -76255,7 +76255,7 @@
         <v>45951</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -76328,7 +76328,7 @@
         <v>45743</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -76401,7 +76401,7 @@
         <v>46286</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -76474,7 +76474,7 @@
         <v>45216</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -76547,7 +76547,7 @@
         <v>45140</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -76620,7 +76620,7 @@
         <v>44651</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -76693,7 +76693,7 @@
         <v>45442</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -76771,7 +76771,7 @@
         <v>44785</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -76844,7 +76844,7 @@
         <v>46246</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -76917,7 +76917,7 @@
         <v>44785</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -76990,7 +76990,7 @@
         <v>46175</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -77063,7 +77063,7 @@
         <v>44929</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -77136,7 +77136,7 @@
         <v>44509</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -77209,7 +77209,7 @@
         <v>46150</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -77282,7 +77282,7 @@
         <v>45740</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -77360,7 +77360,7 @@
         <v>45016</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -77433,7 +77433,7 @@
         <v>44756</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -77506,7 +77506,7 @@
         <v>45448</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -77584,7 +77584,7 @@
         <v>46209</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -77657,7 +77657,7 @@
         <v>45671</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -77730,7 +77730,7 @@
         <v>44589</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -77808,7 +77808,7 @@
         <v>46290</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -77886,7 +77886,7 @@
         <v>44867</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -77964,7 +77964,7 @@
         <v>46105</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -78042,7 +78042,7 @@
         <v>46035</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -78115,7 +78115,7 @@
         <v>44851</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -78188,7 +78188,7 @@
         <v>46249</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -78266,7 +78266,7 @@
         <v>44783</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -78339,7 +78339,7 @@
         <v>46290</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -78417,7 +78417,7 @@
         <v>46290</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -78495,7 +78495,7 @@
         <v>44888</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -78568,7 +78568,7 @@
         <v>46251</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -78641,7 +78641,7 @@
         <v>46048</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -78714,7 +78714,7 @@
         <v>45187</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -78787,7 +78787,7 @@
         <v>44512</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -78880,7 +78880,7 @@
         <v>46295</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -78958,7 +78958,7 @@
         <v>45610</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -79036,7 +79036,7 @@
         <v>45723</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -79109,7 +79109,7 @@
         <v>44964</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -79182,7 +79182,7 @@
         <v>46252</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -79255,7 +79255,7 @@
         <v>45153</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -79328,7 +79328,7 @@
         <v>44672</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -79406,7 +79406,7 @@
         <v>46294</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -79479,7 +79479,7 @@
         <v>45077</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -79552,7 +79552,7 @@
         <v>45306</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -79625,7 +79625,7 @@
         <v>45306</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -79698,7 +79698,7 @@
         <v>44946</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -79771,7 +79771,7 @@
         <v>45537</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -79849,7 +79849,7 @@
         <v>46217</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -79922,7 +79922,7 @@
         <v>46253</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -79995,7 +79995,7 @@
         <v>45301</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -80068,7 +80068,7 @@
         <v>46296</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -80141,7 +80141,7 @@
         <v>45988</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -80219,7 +80219,7 @@
         <v>45362</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -80292,7 +80292,7 @@
         <v>46183</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -80365,7 +80365,7 @@
         <v>46195</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -80458,7 +80458,7 @@
         <v>45036</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -80531,7 +80531,7 @@
         <v>46300</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -80609,7 +80609,7 @@
         <v>44904</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -80682,7 +80682,7 @@
         <v>46301</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -80760,7 +80760,7 @@
         <v>45194</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -80838,7 +80838,7 @@
         <v>45194</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -80916,7 +80916,7 @@
         <v>46300</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -80994,7 +80994,7 @@
         <v>45777</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -81067,7 +81067,7 @@
         <v>45551</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -81140,7 +81140,7 @@
         <v>46300</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -81218,7 +81218,7 @@
         <v>46300</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -81296,7 +81296,7 @@
         <v>46300</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -81374,7 +81374,7 @@
         <v>46301</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -81447,7 +81447,7 @@
         <v>46300</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -81525,7 +81525,7 @@
         <v>46300</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -81603,7 +81603,7 @@
         <v>45476</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -81676,7 +81676,7 @@
         <v>45604</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -81754,7 +81754,7 @@
         <v>45625</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -81832,7 +81832,7 @@
         <v>46189</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -81905,7 +81905,7 @@
         <v>46259</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -81983,7 +81983,7 @@
         <v>46303</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -82056,7 +82056,7 @@
         <v>45793</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -82134,7 +82134,7 @@
         <v>46262</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -82212,7 +82212,7 @@
         <v>46262</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -82290,7 +82290,7 @@
         <v>46262</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -82368,7 +82368,7 @@
         <v>46262</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -82446,7 +82446,7 @@
         <v>45790</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -82519,7 +82519,7 @@
         <v>46261</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -82597,7 +82597,7 @@
         <v>46261</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -82675,7 +82675,7 @@
         <v>46262</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -82753,7 +82753,7 @@
         <v>46261</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -82831,7 +82831,7 @@
         <v>45749</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -82904,7 +82904,7 @@
         <v>46261</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -82982,7 +82982,7 @@
         <v>45561</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -83060,7 +83060,7 @@
         <v>46261</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -83138,7 +83138,7 @@
         <v>46261</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -83216,7 +83216,7 @@
         <v>45799</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -83289,7 +83289,7 @@
         <v>46262</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -83367,7 +83367,7 @@
         <v>46262</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -83445,7 +83445,7 @@
         <v>46262</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -83523,7 +83523,7 @@
         <v>45706</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -83596,7 +83596,7 @@
         <v>45393</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -83669,7 +83669,7 @@
         <v>45287</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -83747,7 +83747,7 @@
         <v>46262</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -83825,7 +83825,7 @@
         <v>46261</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -83903,7 +83903,7 @@
         <v>44956</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -83976,7 +83976,7 @@
         <v>45807</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -84049,7 +84049,7 @@
         <v>46308</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -84122,7 +84122,7 @@
         <v>45810</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -84195,7 +84195,7 @@
         <v>46310</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -84268,7 +84268,7 @@
         <v>45813</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -84341,7 +84341,7 @@
         <v>46310</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -84419,7 +84419,7 @@
         <v>46269</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -84492,7 +84492,7 @@
         <v>45819</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -84565,7 +84565,7 @@
         <v>45825</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -84638,7 +84638,7 @@
         <v>45831</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -84711,7 +84711,7 @@
         <v>45831</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -84784,7 +84784,7 @@
         <v>45793</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -84857,7 +84857,7 @@
         <v>45838</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -84930,7 +84930,7 @@
         <v>45838</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -85003,7 +85003,7 @@
         <v>45790</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -85076,7 +85076,7 @@
         <v>45847</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -85149,7 +85149,7 @@
         <v>45848</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -85222,7 +85222,7 @@
         <v>45849</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -85295,7 +85295,7 @@
         <v>45817</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -85368,7 +85368,7 @@
         <v>45719</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -85441,7 +85441,7 @@
         <v>45853</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -85514,7 +85514,7 @@
         <v>45783</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -85587,7 +85587,7 @@
         <v>44977</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -85660,7 +85660,7 @@
         <v>45775</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -85733,7 +85733,7 @@
         <v>45877</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -85806,7 +85806,7 @@
         <v>45631</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -85879,7 +85879,7 @@
         <v>45525</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -85952,7 +85952,7 @@
         <v>45055</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -86030,7 +86030,7 @@
         <v>45061</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -86103,7 +86103,7 @@
         <v>45531</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -86181,7 +86181,7 @@
         <v>44783</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -86259,7 +86259,7 @@
         <v>44698</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -86332,7 +86332,7 @@
         <v>45545</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -86410,7 +86410,7 @@
         <v>45467</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -86488,7 +86488,7 @@
         <v>44711</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -86561,7 +86561,7 @@
         <v>44487</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -86639,7 +86639,7 @@
         <v>45670</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -86712,7 +86712,7 @@
         <v>45351</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -86790,7 +86790,7 @@
         <v>44671</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -86863,7 +86863,7 @@
         <v>45371</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -86941,7 +86941,7 @@
         <v>45371</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -87019,7 +87019,7 @@
         <v>45637</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -87092,7 +87092,7 @@
         <v>45525</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -87170,7 +87170,7 @@
         <v>45604</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -87243,7 +87243,7 @@
         <v>45341</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -87316,7 +87316,7 @@
         <v>45422</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -87394,7 +87394,7 @@
         <v>45587</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -87467,7 +87467,7 @@
         <v>45332</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -87540,7 +87540,7 @@
         <v>45222</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -87613,7 +87613,7 @@
         <v>44494</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -87686,7 +87686,7 @@
         <v>45785</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -87759,7 +87759,7 @@
         <v>45797</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -87832,7 +87832,7 @@
         <v>45821</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -87905,7 +87905,7 @@
         <v>45834</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -87983,7 +87983,7 @@
         <v>45848</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -88056,7 +88056,7 @@
         <v>45937</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -88134,7 +88134,7 @@
         <v>45937</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -88212,7 +88212,7 @@
         <v>45961</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -88290,7 +88290,7 @@
         <v>45961</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -88368,7 +88368,7 @@
         <v>45961</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -88446,7 +88446,7 @@
         <v>44706</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -88519,7 +88519,7 @@
         <v>46057</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -88597,7 +88597,7 @@
         <v>46085</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -88675,7 +88675,7 @@
         <v>46094</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -88753,7 +88753,7 @@
         <v>46191</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -88831,7 +88831,7 @@
         <v>46270</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -88904,7 +88904,7 @@
         <v>46246</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -88982,7 +88982,7 @@
         <v>46303</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -89055,7 +89055,7 @@
         <v>46262</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -89133,7 +89133,7 @@
         <v>46262</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>

--- a/Översikt VÄSTERVIK.xlsx
+++ b/Översikt VÄSTERVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45461</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45824</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45680</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>44902</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44610</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>44896</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>45558</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45084</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>45908</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44498</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>44699</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>45643</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45475</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45740</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44883</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>45112</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44699</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>45055</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>45936</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45877</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>45475</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45790</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>45755</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45267</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44896</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45726</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45244</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45947</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>46084</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>45531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>45467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45740</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>45525</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45204</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>44610</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>46262</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>45471</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>46098</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45505</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45671</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45974</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45908</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>45973</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>45505</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>46259</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44497</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44505</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45908</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>45471</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>46199</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45671</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>45988</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45055</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>46154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45961</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>46073</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>45638</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>46293</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>45974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>45978</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45686</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45435</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>44868</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>45467</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45961</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>44539</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45363</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>45691</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>46171</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44904</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>45961</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>45635</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45677</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45996</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45608</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45931</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>44935</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45237</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44795</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45233</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>45961</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>46154</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45938</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45961</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45971</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>45985</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>45604</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>46303</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>46308</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45502</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>46279</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>46086</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44931</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45000</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>45615</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44963</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>45055</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45961</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44785</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45853</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45253</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45673</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>46174</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45722</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>45699</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45952</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45961</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45309</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>46001</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44896</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45908</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45985</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>46174</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>46150</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>46105</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45848</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45471</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45303</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>46269</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45233</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>45011</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45376</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45274</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45204</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45055</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45961</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>45355</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>45303</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>45590</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45939</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45135</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45266</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>46196</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>46199</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>45274</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45898</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46217</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44812</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45635</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>46011</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>45533</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>46066</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>46290</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45834</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>45996</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45877</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44946</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45301</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>46189</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45973</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>46302</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46238</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>46197</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>45924</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45611</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45611</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>46086</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>46084</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>46035</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45475</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45740</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44931</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45180</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44887</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45187</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45666</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45194</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45314</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44904</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45455</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>45552</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44522</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45503</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45418</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45321</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44697</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44904</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>44935</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45688</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>44848</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45937</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45937</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>45722</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44851</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45958</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45982</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45985</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45376</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45103</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45244</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>46209</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45992</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45740</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45530</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45266</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>46098</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45777</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45477</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>46296</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45362</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>46205</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>46105</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>46105</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44845</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>44979</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45681</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>46114</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45474</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45870</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45740</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45945</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45555</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>44943</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45201</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45371</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>46147</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>46147</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45089</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45140</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>45238</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45355</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45121</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45671</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44547</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>44729</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45302</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45301</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45301</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44494</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>44904</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>44699</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45055</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44981</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>45435</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>45467</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45762</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45722</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45937</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46105</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44621</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>45917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45918</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45700</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45232</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>44848</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44848</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>46175</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45688</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>45068</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>45958</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>46184</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>46184</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>45468</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>45961</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>45961</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>45961</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>44979</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45966</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45604</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44935</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45980</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>44931</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45625</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>45985</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>45740</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45253</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>45936</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45338</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>46238</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>46240</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>45740</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>46029</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>46044</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45831</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>46300</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>44848</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>46105</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46105</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>46105</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>44944</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>46126</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>45677</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>45782</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45918</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>46266</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45831</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45931</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>46241</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45754</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>44734</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45266</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45754</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>45622</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>45359</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45089</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44631</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44830</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>45740</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45152</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45740</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45336</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45121</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44910</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>45133</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45133</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>44825</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45148</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45700</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45681</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45407</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>44908</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>44715</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44699</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44596</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>45188</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45082</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45055</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45384</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>44981</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45055</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>45531</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>45385</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>44494</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45722</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>45740</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45740</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45789</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45809</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45961</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45961</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45961</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45965</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45966</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>46105</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>46147</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>46177</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46246</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>44582</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>44683</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>44820</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>44873</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>44512</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>44650</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>44755</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>44621</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>44546</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>44851</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44673</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>44851</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -40896,7 +40896,7 @@
         <v>44504</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44887</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44586</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>44861</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44588</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>44564</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>44511</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44501</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -41490,7 +41490,7 @@
         <v>44825</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>44565</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>44848</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>44812</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>44545</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44795</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>44796</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44565</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>44595</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>44756</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>44867</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>44825</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44571</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>44498</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45187</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45301</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45194</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45194</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -42824,7 +42824,7 @@
         <v>45327</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>45140</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>44987</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>45202</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>44623</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>44916</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45894</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>45331</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -43423,7 +43423,7 @@
         <v>44963</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>45256</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45343</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>45204</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         <v>45355</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>45701</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>44930</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>46160</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>46160</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>46160</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>46160</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>46160</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>44848</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45764</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>45673</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45040</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45104</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45873</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45021</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45740</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45379</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>45222</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>44532</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>44964</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45016</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>44539</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44924</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>45036</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44847</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45282</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45282</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>45540</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -45829,7 +45829,7 @@
         <v>44977</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>44977</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -45975,7 +45975,7 @@
         <v>45374</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         <v>45937</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45937</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45937</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -46282,7 +46282,7 @@
         <v>44512</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45160</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>45036</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>46175</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45939</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45939</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45104</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>45722</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>45160</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>45379</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45302</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45460</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>45610</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>44929</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>45301</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45301</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>44908</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45442</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>45117</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45086</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>45950</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45950</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>45947</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45950</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>44942</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>45454</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45952</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45160</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45622</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>44785</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -48537,7 +48537,7 @@
         <v>44641</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -48615,7 +48615,7 @@
         <v>45953</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>45953</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45953</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -48834,7 +48834,7 @@
         <v>45035</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
         <v>45253</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45147</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45022</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -49131,7 +49131,7 @@
         <v>45643</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45959</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>46184</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>46184</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>45012</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45590</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>46184</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>46184</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>46184</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45455</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>45460</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>44989</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>45961</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>46189</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45961</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>45961</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>44979</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -50422,7 +50422,7 @@
         <v>45260</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>45448</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>44783</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -50646,7 +50646,7 @@
         <v>44728</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>46190</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -50792,7 +50792,7 @@
         <v>45631</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>46195</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>46195</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45414</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45971</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45916</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>45743</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -51308,7 +51308,7 @@
         <v>45971</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -51386,7 +51386,7 @@
         <v>45148</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>46197</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -51537,7 +51537,7 @@
         <v>45968</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>46197</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -51688,7 +51688,7 @@
         <v>45567</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -51761,7 +51761,7 @@
         <v>44960</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>44979</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -51907,7 +51907,7 @@
         <v>45215</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45003</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -52073,7 +52073,7 @@
         <v>44979</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>44532</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         <v>45978</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>46199</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -52375,7 +52375,7 @@
         <v>44785</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -52448,7 +52448,7 @@
         <v>46199</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>45371</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>45240</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -52672,7 +52672,7 @@
         <v>44888</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -52745,7 +52745,7 @@
         <v>45611</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>45477</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -52896,7 +52896,7 @@
         <v>46202</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -52969,7 +52969,7 @@
         <v>45982</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>46205</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         <v>46205</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>44756</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>45985</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>44861</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -53407,7 +53407,7 @@
         <v>45985</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -53480,7 +53480,7 @@
         <v>45986</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>46205</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45985</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>45985</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -53782,7 +53782,7 @@
         <v>45986</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -53860,7 +53860,7 @@
         <v>45477</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45985</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>46029</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -54084,7 +54084,7 @@
         <v>45945</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -54157,7 +54157,7 @@
         <v>45694</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>45036</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45596</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -54376,7 +54376,7 @@
         <v>45988</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>44973</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -54522,7 +54522,7 @@
         <v>45160</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -54595,7 +54595,7 @@
         <v>45256</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -54673,7 +54673,7 @@
         <v>45994</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -54746,7 +54746,7 @@
         <v>45258</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>46217</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>46217</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>46217</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45740</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -55116,7 +55116,7 @@
         <v>46001</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -55194,7 +55194,7 @@
         <v>46001</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -55272,7 +55272,7 @@
         <v>46001</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -55350,7 +55350,7 @@
         <v>45551</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45777</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>46008</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -55569,7 +55569,7 @@
         <v>46008</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -55642,7 +55642,7 @@
         <v>46008</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>46008</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>46008</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -55861,7 +55861,7 @@
         <v>46008</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -55934,7 +55934,7 @@
         <v>46008</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>46008</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45512</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>45512</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -56226,7 +56226,7 @@
         <v>45476</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -56299,7 +56299,7 @@
         <v>46234</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>46013</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>46013</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>46013</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>46013</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>46013</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -56767,7 +56767,7 @@
         <v>46238</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
         <v>46239</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>46238</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>45625</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45604</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -57142,7 +57142,7 @@
         <v>46020</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>46238</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>46238</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>46238</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -57434,7 +57434,7 @@
         <v>46238</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>46238</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>45842</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -57653,7 +57653,7 @@
         <v>44881</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -57726,7 +57726,7 @@
         <v>46030</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>46286</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>46034</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>46034</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>46034</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -58096,7 +58096,7 @@
         <v>46034</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -58169,7 +58169,7 @@
         <v>46183</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -58242,7 +58242,7 @@
         <v>46282</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -58315,7 +58315,7 @@
         <v>45951</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -58388,7 +58388,7 @@
         <v>45793</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>46044</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -58539,7 +58539,7 @@
         <v>46044</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -58612,7 +58612,7 @@
         <v>46044</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>46042</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -58758,7 +58758,7 @@
         <v>46044</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -58831,7 +58831,7 @@
         <v>46044</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -58904,7 +58904,7 @@
         <v>46044</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45790</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -59050,7 +59050,7 @@
         <v>46044</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -59123,7 +59123,7 @@
         <v>46246</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -59196,7 +59196,7 @@
         <v>45706</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -59269,7 +59269,7 @@
         <v>45799</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -59342,7 +59342,7 @@
         <v>45749</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -59415,7 +59415,7 @@
         <v>45561</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>45393</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -59566,7 +59566,7 @@
         <v>46150</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>44956</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -59712,7 +59712,7 @@
         <v>45287</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -59790,7 +59790,7 @@
         <v>46051</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -59868,7 +59868,7 @@
         <v>46035</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -59941,7 +59941,7 @@
         <v>46290</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -60019,7 +60019,7 @@
         <v>46175</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>46105</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -60170,7 +60170,7 @@
         <v>46055</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>45810</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -60316,7 +60316,7 @@
         <v>46048</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>45807</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -60462,7 +60462,7 @@
         <v>46290</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -60540,7 +60540,7 @@
         <v>46290</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -60618,7 +60618,7 @@
         <v>46059</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -60691,7 +60691,7 @@
         <v>46294</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -60764,7 +60764,7 @@
         <v>45813</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>46251</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -60910,7 +60910,7 @@
         <v>45483</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>46249</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -61061,7 +61061,7 @@
         <v>44946</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -61134,7 +61134,7 @@
         <v>46209</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -61207,7 +61207,7 @@
         <v>45819</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>46253</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -61353,7 +61353,7 @@
         <v>46296</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -61426,7 +61426,7 @@
         <v>45825</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>46252</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45831</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>46295</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -61723,7 +61723,7 @@
         <v>45988</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -61801,7 +61801,7 @@
         <v>45831</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -61874,7 +61874,7 @@
         <v>46217</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45793</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -62020,7 +62020,7 @@
         <v>46300</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -62098,7 +62098,7 @@
         <v>46300</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -62176,7 +62176,7 @@
         <v>46300</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -62254,7 +62254,7 @@
         <v>45838</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -62327,7 +62327,7 @@
         <v>46300</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -62405,7 +62405,7 @@
         <v>46300</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -62483,7 +62483,7 @@
         <v>45838</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -62556,7 +62556,7 @@
         <v>45530</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -62634,7 +62634,7 @@
         <v>46195</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -62727,7 +62727,7 @@
         <v>45790</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -62800,7 +62800,7 @@
         <v>44937</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -62873,7 +62873,7 @@
         <v>46300</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -62951,7 +62951,7 @@
         <v>46300</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -63029,7 +63029,7 @@
         <v>46183</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -63102,7 +63102,7 @@
         <v>45848</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -63175,7 +63175,7 @@
         <v>45566</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -63248,7 +63248,7 @@
         <v>46259</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -63326,7 +63326,7 @@
         <v>46301</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -63404,7 +63404,7 @@
         <v>45847</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         <v>45849</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -63550,7 +63550,7 @@
         <v>45719</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -63623,7 +63623,7 @@
         <v>45817</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -63696,7 +63696,7 @@
         <v>45853</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -63769,7 +63769,7 @@
         <v>46113</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -63847,7 +63847,7 @@
         <v>46113</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -63920,7 +63920,7 @@
         <v>46301</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -63993,7 +63993,7 @@
         <v>46261</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -64071,7 +64071,7 @@
         <v>46303</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -64144,7 +64144,7 @@
         <v>46113</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -64217,7 +64217,7 @@
         <v>45783</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -64290,7 +64290,7 @@
         <v>44977</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -64363,7 +64363,7 @@
         <v>46261</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -64441,7 +64441,7 @@
         <v>46261</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -64519,7 +64519,7 @@
         <v>46261</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -64597,7 +64597,7 @@
         <v>44564</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>44564</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
         <v>46261</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -64821,7 +64821,7 @@
         <v>46261</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -64899,7 +64899,7 @@
         <v>45775</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -64972,7 +64972,7 @@
         <v>45635</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -65045,7 +65045,7 @@
         <v>46189</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>46262</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -65196,7 +65196,7 @@
         <v>46261</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -65274,7 +65274,7 @@
         <v>44589</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -65352,7 +65352,7 @@
         <v>46128</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -65425,7 +65425,7 @@
         <v>45877</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -65498,7 +65498,7 @@
         <v>46132</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -65576,7 +65576,7 @@
         <v>46132</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -65654,7 +65654,7 @@
         <v>46262</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -65732,7 +65732,7 @@
         <v>46262</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -65810,7 +65810,7 @@
         <v>45460</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -65883,7 +65883,7 @@
         <v>45535</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -65956,7 +65956,7 @@
         <v>45321</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -66029,7 +66029,7 @@
         <v>44912</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -66107,7 +66107,7 @@
         <v>44912</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -66185,7 +66185,7 @@
         <v>45625</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         <v>46262</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -66341,7 +66341,7 @@
         <v>45754</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -66419,7 +66419,7 @@
         <v>44867</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -66497,7 +66497,7 @@
         <v>45538</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -66570,7 +66570,7 @@
         <v>46029</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45784</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -66716,7 +66716,7 @@
         <v>46262</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -66794,7 +66794,7 @@
         <v>46262</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -66872,7 +66872,7 @@
         <v>46262</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -66950,7 +66950,7 @@
         <v>46262</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -67028,7 +67028,7 @@
         <v>46262</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -67106,7 +67106,7 @@
         <v>45818</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -67179,7 +67179,7 @@
         <v>45842</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -67252,7 +67252,7 @@
         <v>45793</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -67325,7 +67325,7 @@
         <v>45931</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -67398,7 +67398,7 @@
         <v>45272</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -67471,7 +67471,7 @@
         <v>46308</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -67544,7 +67544,7 @@
         <v>45714</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>46310</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -67695,7 +67695,7 @@
         <v>44964</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -67768,7 +67768,7 @@
         <v>45622</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -67841,7 +67841,7 @@
         <v>46310</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -67919,7 +67919,7 @@
         <v>45463</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -67997,7 +67997,7 @@
         <v>45643</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -68070,7 +68070,7 @@
         <v>44748</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -68148,7 +68148,7 @@
         <v>45300</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -68221,7 +68221,7 @@
         <v>45511</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -68299,7 +68299,7 @@
         <v>45939</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -68372,7 +68372,7 @@
         <v>45883</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -68445,7 +68445,7 @@
         <v>45945</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -68523,7 +68523,7 @@
         <v>44595</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -68596,7 +68596,7 @@
         <v>46272</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -68669,7 +68669,7 @@
         <v>46272</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -68742,7 +68742,7 @@
         <v>44672</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -68820,7 +68820,7 @@
         <v>45791</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -68893,7 +68893,7 @@
         <v>46272</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -68966,7 +68966,7 @@
         <v>45804</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -69039,7 +69039,7 @@
         <v>46269</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -69112,7 +69112,7 @@
         <v>45553</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -69185,7 +69185,7 @@
         <v>45529</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -69258,7 +69258,7 @@
         <v>45939</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -69331,7 +69331,7 @@
         <v>45391</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -69409,7 +69409,7 @@
         <v>45817</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -69482,7 +69482,7 @@
         <v>45531</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -69555,7 +69555,7 @@
         <v>45117</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -69628,7 +69628,7 @@
         <v>45553</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -69701,7 +69701,7 @@
         <v>46315</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -69779,7 +69779,7 @@
         <v>45358</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -69852,7 +69852,7 @@
         <v>46315</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -69930,7 +69930,7 @@
         <v>45379</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -70003,7 +70003,7 @@
         <v>45321</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -70081,7 +70081,7 @@
         <v>45483</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -70154,7 +70154,7 @@
         <v>46315</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -70232,7 +70232,7 @@
         <v>46315</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -70310,7 +70310,7 @@
         <v>46314</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -70388,7 +70388,7 @@
         <v>46316</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -70461,7 +70461,7 @@
         <v>46315</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -70539,7 +70539,7 @@
         <v>44973</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -70612,7 +70612,7 @@
         <v>45604</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -70690,7 +70690,7 @@
         <v>44973</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -70763,7 +70763,7 @@
         <v>45362</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -70836,7 +70836,7 @@
         <v>46142</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -70914,7 +70914,7 @@
         <v>45589</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -70987,7 +70987,7 @@
         <v>46318</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -71065,7 +71065,7 @@
         <v>45211</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -71143,7 +71143,7 @@
         <v>44904</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -71216,7 +71216,7 @@
         <v>44904</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -71289,7 +71289,7 @@
         <v>46099</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -71362,7 +71362,7 @@
         <v>44904</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -71435,7 +71435,7 @@
         <v>46141</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -71513,7 +71513,7 @@
         <v>45533</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -71591,7 +71591,7 @@
         <v>45576</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -71664,7 +71664,7 @@
         <v>44615</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -71737,7 +71737,7 @@
         <v>46147</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -71815,7 +71815,7 @@
         <v>45371</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -71888,7 +71888,7 @@
         <v>46147</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -71966,7 +71966,7 @@
         <v>46147</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -72044,7 +72044,7 @@
         <v>46147</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -72122,7 +72122,7 @@
         <v>46147</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -72200,7 +72200,7 @@
         <v>45016</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -72273,7 +72273,7 @@
         <v>46120</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -72346,7 +72346,7 @@
         <v>45077</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -72419,7 +72419,7 @@
         <v>44994</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -72492,7 +72492,7 @@
         <v>44970</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -72565,7 +72565,7 @@
         <v>45391</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -72643,7 +72643,7 @@
         <v>45085</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -72721,7 +72721,7 @@
         <v>45121</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -72794,7 +72794,7 @@
         <v>45671</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -72872,7 +72872,7 @@
         <v>45460</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -72945,7 +72945,7 @@
         <v>46160</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -73023,7 +73023,7 @@
         <v>44783</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -73096,7 +73096,7 @@
         <v>44956</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -73174,7 +73174,7 @@
         <v>44946</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -73247,7 +73247,7 @@
         <v>44939</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -73320,7 +73320,7 @@
         <v>45265</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -73393,7 +73393,7 @@
         <v>44776</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -73466,7 +73466,7 @@
         <v>45245</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -73544,7 +73544,7 @@
         <v>45000</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -73622,7 +73622,7 @@
         <v>44720</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -73695,7 +73695,7 @@
         <v>44964</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -73768,7 +73768,7 @@
         <v>44956</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -73841,7 +73841,7 @@
         <v>45642</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -73914,7 +73914,7 @@
         <v>44798</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -73987,7 +73987,7 @@
         <v>45596</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -74060,7 +74060,7 @@
         <v>45204</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -74133,7 +74133,7 @@
         <v>45147</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -74206,7 +74206,7 @@
         <v>44984</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -74279,7 +74279,7 @@
         <v>44984</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -74357,7 +74357,7 @@
         <v>45140</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -74430,7 +74430,7 @@
         <v>45035</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -74503,7 +74503,7 @@
         <v>44655</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -74576,7 +74576,7 @@
         <v>44795</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -74649,7 +74649,7 @@
         <v>45678</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -74722,7 +74722,7 @@
         <v>45202</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -74795,7 +74795,7 @@
         <v>45483</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -74868,7 +74868,7 @@
         <v>44589</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -74941,7 +74941,7 @@
         <v>45740</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -75019,7 +75019,7 @@
         <v>45240</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -75092,7 +75092,7 @@
         <v>45201</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -75165,7 +75165,7 @@
         <v>44851</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -75238,7 +75238,7 @@
         <v>45215</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -75311,7 +75311,7 @@
         <v>44923</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -75384,7 +75384,7 @@
         <v>44923</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -75457,7 +75457,7 @@
         <v>45075</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -75530,7 +75530,7 @@
         <v>45723</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -75603,7 +75603,7 @@
         <v>44977</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -75676,7 +75676,7 @@
         <v>45068</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -75749,7 +75749,7 @@
         <v>45523</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -75822,7 +75822,7 @@
         <v>45076</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -75895,7 +75895,7 @@
         <v>45331</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -75973,7 +75973,7 @@
         <v>44848</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -76051,7 +76051,7 @@
         <v>45754</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -76129,7 +76129,7 @@
         <v>44988</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -76202,7 +76202,7 @@
         <v>44971</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -76275,7 +76275,7 @@
         <v>45035</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -76348,7 +76348,7 @@
         <v>45076</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -76421,7 +76421,7 @@
         <v>45313</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -76494,7 +76494,7 @@
         <v>44980</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -76567,7 +76567,7 @@
         <v>45140</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -76640,7 +76640,7 @@
         <v>44902</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -76713,7 +76713,7 @@
         <v>45089</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -76786,7 +76786,7 @@
         <v>45191</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -76864,7 +76864,7 @@
         <v>45226</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -76942,7 +76942,7 @@
         <v>45740</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -77020,7 +77020,7 @@
         <v>45089</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -77093,7 +77093,7 @@
         <v>44651</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -77166,7 +77166,7 @@
         <v>45740</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -77244,7 +77244,7 @@
         <v>45740</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -77322,7 +77322,7 @@
         <v>45104</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -77395,7 +77395,7 @@
         <v>45049</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -77468,7 +77468,7 @@
         <v>45016</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -77541,7 +77541,7 @@
         <v>45196</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -77619,7 +77619,7 @@
         <v>45161</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -77692,7 +77692,7 @@
         <v>45159</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -77765,7 +77765,7 @@
         <v>44901</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -77838,7 +77838,7 @@
         <v>45330</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -77911,7 +77911,7 @@
         <v>45390</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -77984,7 +77984,7 @@
         <v>45538</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -78057,7 +78057,7 @@
         <v>44944</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -78130,7 +78130,7 @@
         <v>44901</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -78203,7 +78203,7 @@
         <v>44956</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -78276,7 +78276,7 @@
         <v>45201</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -78349,7 +78349,7 @@
         <v>45201</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -78422,7 +78422,7 @@
         <v>45198</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -78495,7 +78495,7 @@
         <v>45093</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -78568,7 +78568,7 @@
         <v>44552</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -78641,7 +78641,7 @@
         <v>44820</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -78714,7 +78714,7 @@
         <v>45306</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -78787,7 +78787,7 @@
         <v>45306</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -78860,7 +78860,7 @@
         <v>44973</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -78933,7 +78933,7 @@
         <v>45035</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -79006,7 +79006,7 @@
         <v>44977</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -79079,7 +79079,7 @@
         <v>45566</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -79152,7 +79152,7 @@
         <v>44910</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -79225,7 +79225,7 @@
         <v>44621</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -79298,7 +79298,7 @@
         <v>45484</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -79371,7 +79371,7 @@
         <v>44977</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -79444,7 +79444,7 @@
         <v>45148</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -79522,7 +79522,7 @@
         <v>45644</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -79600,7 +79600,7 @@
         <v>45133</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -79673,7 +79673,7 @@
         <v>45671</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -79751,7 +79751,7 @@
         <v>45170</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -79824,7 +79824,7 @@
         <v>45170</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -79897,7 +79897,7 @@
         <v>45630</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -79970,7 +79970,7 @@
         <v>45160</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -80048,7 +80048,7 @@
         <v>45537</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -80126,7 +80126,7 @@
         <v>45678</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -80219,7 +80219,7 @@
         <v>45673</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -80292,7 +80292,7 @@
         <v>45068</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -80365,7 +80365,7 @@
         <v>45671</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -80443,7 +80443,7 @@
         <v>45478</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -80516,7 +80516,7 @@
         <v>45468</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -80589,7 +80589,7 @@
         <v>45468</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -80662,7 +80662,7 @@
         <v>45635</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -80735,7 +80735,7 @@
         <v>44646</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -80808,7 +80808,7 @@
         <v>45706</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -80881,7 +80881,7 @@
         <v>45621</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -80959,7 +80959,7 @@
         <v>45049</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -81032,7 +81032,7 @@
         <v>45755</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -81105,7 +81105,7 @@
         <v>45093</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -81178,7 +81178,7 @@
         <v>45093</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -81251,7 +81251,7 @@
         <v>45093</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -81324,7 +81324,7 @@
         <v>45196</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -81402,7 +81402,7 @@
         <v>44669</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -81475,7 +81475,7 @@
         <v>45240</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -81548,7 +81548,7 @@
         <v>45147</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -81621,7 +81621,7 @@
         <v>44573</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -81699,7 +81699,7 @@
         <v>45245</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -81777,7 +81777,7 @@
         <v>45148</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -81855,7 +81855,7 @@
         <v>44623</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -81933,7 +81933,7 @@
         <v>44635</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -82006,7 +82006,7 @@
         <v>45239</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -82079,7 +82079,7 @@
         <v>45147</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -82157,7 +82157,7 @@
         <v>45153</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -82230,7 +82230,7 @@
         <v>45236</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -82303,7 +82303,7 @@
         <v>45211</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -82381,7 +82381,7 @@
         <v>45251</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -82459,7 +82459,7 @@
         <v>45722</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -82532,7 +82532,7 @@
         <v>44722</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -82605,7 +82605,7 @@
         <v>45159</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -82678,7 +82678,7 @@
         <v>45236</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -82756,7 +82756,7 @@
         <v>45216</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -82829,7 +82829,7 @@
         <v>45110</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -82907,7 +82907,7 @@
         <v>45261</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -82985,7 +82985,7 @@
         <v>45525</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -83063,7 +83063,7 @@
         <v>45272</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -83136,7 +83136,7 @@
         <v>45680</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -83209,7 +83209,7 @@
         <v>45336</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -83282,7 +83282,7 @@
         <v>45237</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -83355,7 +83355,7 @@
         <v>45309</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -83428,7 +83428,7 @@
         <v>45369</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -83501,7 +83501,7 @@
         <v>44811</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -83574,7 +83574,7 @@
         <v>45237</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -83647,7 +83647,7 @@
         <v>44785</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -83720,7 +83720,7 @@
         <v>44785</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -83793,7 +83793,7 @@
         <v>45366</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -83871,7 +83871,7 @@
         <v>45196</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -83949,7 +83949,7 @@
         <v>45196</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -84027,7 +84027,7 @@
         <v>45240</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -84100,7 +84100,7 @@
         <v>45477</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -84178,7 +84178,7 @@
         <v>45477</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -84256,7 +84256,7 @@
         <v>45301</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -84329,7 +84329,7 @@
         <v>45301</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -84402,7 +84402,7 @@
         <v>45089</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -84475,7 +84475,7 @@
         <v>45040</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -84548,7 +84548,7 @@
         <v>45301</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -84621,7 +84621,7 @@
         <v>45114</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -84694,7 +84694,7 @@
         <v>45278</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -84767,7 +84767,7 @@
         <v>45301</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -84840,7 +84840,7 @@
         <v>44509</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -84913,7 +84913,7 @@
         <v>45637</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -84986,7 +84986,7 @@
         <v>45631</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -85059,7 +85059,7 @@
         <v>44935</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -85132,7 +85132,7 @@
         <v>44901</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -85205,7 +85205,7 @@
         <v>45671</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -85278,7 +85278,7 @@
         <v>45033</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -85351,7 +85351,7 @@
         <v>44916</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -85424,7 +85424,7 @@
         <v>44893</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -85497,7 +85497,7 @@
         <v>44848</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -85570,7 +85570,7 @@
         <v>44867</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -85648,7 +85648,7 @@
         <v>45489</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -85721,7 +85721,7 @@
         <v>44904</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -85794,7 +85794,7 @@
         <v>44904</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -85867,7 +85867,7 @@
         <v>45174</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -85940,7 +85940,7 @@
         <v>44646</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -86013,7 +86013,7 @@
         <v>44960</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -86086,7 +86086,7 @@
         <v>44698</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -86159,7 +86159,7 @@
         <v>44711</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -86232,7 +86232,7 @@
         <v>44671</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -86305,7 +86305,7 @@
         <v>45631</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -86378,7 +86378,7 @@
         <v>45525</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -86451,7 +86451,7 @@
         <v>45055</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -86529,7 +86529,7 @@
         <v>45061</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -86602,7 +86602,7 @@
         <v>45531</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -86680,7 +86680,7 @@
         <v>44783</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -86758,7 +86758,7 @@
         <v>45545</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -86836,7 +86836,7 @@
         <v>45467</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -86914,7 +86914,7 @@
         <v>45670</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -86987,7 +86987,7 @@
         <v>45351</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -87065,7 +87065,7 @@
         <v>45371</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -87143,7 +87143,7 @@
         <v>45371</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -87221,7 +87221,7 @@
         <v>45637</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -87294,7 +87294,7 @@
         <v>45525</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -87372,7 +87372,7 @@
         <v>45604</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -87445,7 +87445,7 @@
         <v>45341</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -87518,7 +87518,7 @@
         <v>45422</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -87596,7 +87596,7 @@
         <v>45587</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -87669,7 +87669,7 @@
         <v>45332</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -87742,7 +87742,7 @@
         <v>45222</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -87815,7 +87815,7 @@
         <v>44494</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -87888,7 +87888,7 @@
         <v>45785</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -87961,7 +87961,7 @@
         <v>45797</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -88034,7 +88034,7 @@
         <v>45821</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -88107,7 +88107,7 @@
         <v>45834</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -88185,7 +88185,7 @@
         <v>45848</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -88258,7 +88258,7 @@
         <v>45937</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -88336,7 +88336,7 @@
         <v>45937</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -88414,7 +88414,7 @@
         <v>45961</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -88492,7 +88492,7 @@
         <v>45961</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -88570,7 +88570,7 @@
         <v>45961</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -88648,7 +88648,7 @@
         <v>44706</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -88721,7 +88721,7 @@
         <v>46057</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -88799,7 +88799,7 @@
         <v>46085</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -88877,7 +88877,7 @@
         <v>46094</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -88955,7 +88955,7 @@
         <v>46191</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -89033,7 +89033,7 @@
         <v>46246</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -89111,7 +89111,7 @@
         <v>46262</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -89189,7 +89189,7 @@
         <v>46262</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -89267,7 +89267,7 @@
         <v>46303</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -89340,7 +89340,7 @@
         <v>46270</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
